--- a/results/openset_pivot.xlsx
+++ b/results/openset_pivot.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W108"/>
+  <dimension ref="A1:W124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,14 +785,30 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2310855173976649</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1846500385074279</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.6954403063000348</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.3375262859627878</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3276523818882649</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.4856348470806302</v>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -824,14 +840,30 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0.5885</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3303673802612091</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.292578170042027</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.7082594824530308</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.5365</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.517916358990929</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.5170685888308306</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5306329113924051</v>
+      </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -952,38 +984,26 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>SCL</t>
-        </is>
-      </c>
+      <c r="B12" s="1" t="n"/>
       <c r="C12" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9985000000000001</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9974156791918124</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9971014492753624</v>
+        <v>91.19</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9989868287740628</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
+        <v>94.27</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -999,26 +1019,38 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
-      <c r="B13" s="1" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
       <c r="C13" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9925</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9863216066526403</v>
+        <v>0.9974156791918124</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9845796345085081</v>
+        <v>0.9971014492753624</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9950314673733024</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+        <v>0.9989868287740628</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1034,54 +1066,34 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>ab</t>
-        </is>
-      </c>
+      <c r="B14" s="1" t="n"/>
       <c r="C14" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>78.7</v>
+        <v>0.9925</v>
       </c>
       <c r="E14" t="n">
-        <v>60.3</v>
+        <v>0.9863216066526403</v>
       </c>
       <c r="F14" t="n">
-        <v>55</v>
+        <v>0.9845796345085081</v>
       </c>
       <c r="G14" t="n">
-        <v>86.90000000000001</v>
+        <v>0.9950314673733024</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="N14" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="O14" t="n">
-        <v>65</v>
-      </c>
-      <c r="P14" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="S14" t="n">
-        <v>46.2</v>
-      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
@@ -1089,34 +1101,54 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="1" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
       <c r="C15" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>71.8</v>
+        <v>78.7</v>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>60.3</v>
       </c>
       <c r="F15" t="n">
-        <v>54.7</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>80.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="N15" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>65</v>
+      </c>
+      <c r="P15" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="S15" t="n">
+        <v>46.2</v>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1124,124 +1156,132 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B16" s="1" t="n"/>
       <c r="C16" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>93.75</v>
+        <v>71.8</v>
       </c>
       <c r="E16" t="n">
-        <v>92.4755</v>
+        <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>54.7</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>80.5</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="M16" t="n">
-        <v>86.2758</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>89.45</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>93.517</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>DBPedia</t>
-        </is>
-      </c>
+      <c r="A17" s="1" t="n"/>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>82.6465</v>
-      </c>
-      <c r="J17" t="n">
-        <v>82.6126</v>
-      </c>
-      <c r="K17" t="n">
-        <v>84.5119</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="E17" t="n">
+        <v>92.4755</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.2758</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>89.45</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>93.517</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>DBPedia</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
       <c r="C18" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>61.85</v>
+        <v>56.65</v>
       </c>
       <c r="E18" t="n">
-        <v>33.4901</v>
+        <v>55.2909</v>
       </c>
       <c r="F18" t="n">
-        <v>32.7621</v>
+        <v>55.1777</v>
       </c>
       <c r="G18" t="n">
-        <v>73.5273</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+        <v>61.5156</v>
+      </c>
+      <c r="H18" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>82.6465</v>
+      </c>
+      <c r="J18" t="n">
+        <v>82.6126</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.5119</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -1257,25 +1297,21 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
+      <c r="B19" s="1" t="n"/>
       <c r="C19" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6565</v>
+        <v>61.85</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0141541977491268</v>
+        <v>33.4901</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>32.7621</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7926350739511017</v>
+        <v>73.5273</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1298,36 +1334,52 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C20" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.222</v>
+        <v>0.6565</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2819008164440028</v>
+        <v>0.0141541977491268</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2842347838576091</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1535326086956521</v>
+        <v>0.7926350739511017</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.0045667167727638</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.5069055617767824</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.0012306351928993</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.2030548068283917</v>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -1337,36 +1389,52 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C21" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7035</v>
+        <v>0.222</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7643760721302792</v>
+        <v>0.2819008164440028</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7651338724230047</v>
+        <v>0.2842347838576091</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7226970560303894</v>
+        <v>0.1535326086956521</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2807982583591505</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.2824583223945039</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0981912144702842</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.2437282403341855</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2444819483842712</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1201201201201201</v>
+      </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
@@ -1374,21 +1442,25 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="1" t="n"/>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
       <c r="C22" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6975</v>
+        <v>0.7035</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6270908001133587</v>
+        <v>0.7643760721302792</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6243382934937298</v>
+        <v>0.7651338724230047</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7784786641929499</v>
+        <v>0.7226970560303894</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1409,25 +1481,21 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>KnnCon</t>
-        </is>
-      </c>
+      <c r="B23" s="1" t="n"/>
       <c r="C23" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>86.59999999999999</v>
+        <v>0.6975</v>
       </c>
       <c r="E23" t="n">
-        <v>79.83</v>
+        <v>0.6270908001133587</v>
       </c>
       <c r="F23" t="n">
-        <v>79.65000000000001</v>
+        <v>0.6243382934937298</v>
       </c>
       <c r="G23" t="n">
-        <v>89.44</v>
+        <v>0.7784786641929499</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1450,28 +1518,28 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="n">
-        <v>0.7445000000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.563541059873655</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.5590021957840905</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.8131785847997005</v>
-      </c>
+      <c r="D24" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="E24" t="n">
+        <v>79.83</v>
+      </c>
+      <c r="F24" t="n">
+        <v>79.65000000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>89.44</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -1487,54 +1555,34 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>ab</t>
-        </is>
-      </c>
+      <c r="B25" s="1" t="n"/>
       <c r="C25" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>70.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="E25" t="n">
-        <v>31.5</v>
+        <v>48.14</v>
       </c>
       <c r="F25" t="n">
-        <v>30.6</v>
+        <v>47.57</v>
       </c>
       <c r="G25" t="n">
-        <v>81.09999999999999</v>
+        <v>79.25</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="N25" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="P25" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S25" t="n">
-        <v>24.7</v>
-      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
@@ -1542,26 +1590,38 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="1" t="n"/>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
       <c r="C26" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>82.40000000000001</v>
+        <v>0.6595</v>
       </c>
       <c r="E26" t="n">
-        <v>14.5</v>
+        <v>0.0265514934932747</v>
       </c>
       <c r="F26" t="n">
-        <v>13.2</v>
+        <v>0.0125965537730243</v>
       </c>
       <c r="G26" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+        <v>0.7940731781070457</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.7445000000000001</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.563541059873655</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5590021957840905</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.8131785847997005</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -1576,35 +1636,27 @@
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>TREC</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>ADB</t>
-        </is>
-      </c>
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="1" t="n"/>
       <c r="C27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
-        <v>80.41</v>
-      </c>
-      <c r="I27" t="n">
-        <v>83.67140000000001</v>
-      </c>
-      <c r="J27" t="n">
-        <v>85.21259999999999</v>
-      </c>
-      <c r="K27" t="n">
-        <v>68.2594</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0159935315926481</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.8956377691882937</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -1622,36 +1674,52 @@
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C28" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6775510204081633</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3748318533937143</v>
+        <v>31.5</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3486334466932848</v>
+        <v>30.6</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6368159203980099</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="N28" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="S28" t="n">
+        <v>24.7</v>
+      </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
@@ -1659,25 +1727,21 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>DeepUnk</t>
-        </is>
-      </c>
+      <c r="B29" s="1" t="n"/>
       <c r="C29" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4693877551020408</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2850229038482891</v>
+        <v>14.5</v>
       </c>
       <c r="F29" t="n">
-        <v>0.26323272884383</v>
+        <v>13.2</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5247148288973384</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1697,31 +1761,43 @@
       <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n"/>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>TREC</t>
+        </is>
+      </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C30" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7122448979591837</v>
+        <v>63.27</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6866140378665598</v>
+        <v>47.6811</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7216630168710466</v>
+        <v>48.4663</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3010752688172043</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+        <v>39.0438</v>
+      </c>
+      <c r="H30" t="n">
+        <v>80.41</v>
+      </c>
+      <c r="I30" t="n">
+        <v>83.67140000000001</v>
+      </c>
+      <c r="J30" t="n">
+        <v>85.21259999999999</v>
+      </c>
+      <c r="K30" t="n">
+        <v>68.2594</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -1739,36 +1815,52 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C31" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>80.2</v>
+        <v>0.6775510204081633</v>
       </c>
       <c r="E31" t="n">
-        <v>84.87</v>
+        <v>0.3748318533937143</v>
       </c>
       <c r="F31" t="n">
-        <v>87.22</v>
+        <v>0.3486334466932848</v>
       </c>
       <c r="G31" t="n">
-        <v>61.41</v>
+        <v>0.6368159203980099</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0.1591836734693877</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.0119412124923453</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.2746478873239437</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.5612244897959183</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.2529310838927908</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.252249051951459</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.2740740740740741</v>
+      </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
@@ -1778,51 +1870,51 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>50.8</v>
+        <v>0.4693877551020408</v>
       </c>
       <c r="E32" t="n">
-        <v>36.5</v>
+        <v>0.2850229038482891</v>
       </c>
       <c r="F32" t="n">
-        <v>36.5</v>
+        <v>0.26323272884383</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.5247148288973384</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>43.1</v>
+        <v>0.4653061224489795</v>
       </c>
       <c r="M32" t="n">
-        <v>22.8</v>
+        <v>0.3065925054437858</v>
       </c>
       <c r="N32" t="n">
-        <v>22.8</v>
+        <v>0.3044206160716554</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>0.3565459610027855</v>
       </c>
       <c r="P32" t="n">
-        <v>38</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="Q32" t="n">
-        <v>17.6</v>
+        <v>0.1792102670353817</v>
       </c>
       <c r="R32" t="n">
-        <v>17.6</v>
+        <v>0.1789512128802374</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -1830,35 +1922,31 @@
       <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>Yahoo</t>
-        </is>
-      </c>
+      <c r="A33" s="1" t="n"/>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C33" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>59.4906</v>
-      </c>
-      <c r="J33" t="n">
-        <v>52.9492</v>
-      </c>
-      <c r="K33" t="n">
-        <v>72.5732</v>
-      </c>
+      <c r="D33" t="n">
+        <v>0.7122448979591837</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6866140378665598</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.7216630168710466</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.3010752688172043</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -1874,25 +1962,21 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
+      <c r="B34" s="1" t="n"/>
       <c r="C34" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.8020408163265306</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3609324594969105</v>
+        <v>0.3849081787305231</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1616352201257861</v>
+        <v>0.3434723171565277</v>
       </c>
       <c r="G34" t="n">
-        <v>0.759526938239159</v>
+        <v>0.8821385176184691</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1915,23 +1999,23 @@
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C35" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.776</v>
+        <v>80.2</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4685069098477059</v>
+        <v>84.87</v>
       </c>
       <c r="F35" t="n">
-        <v>0.268814867141227</v>
+        <v>87.22</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8678909952606635</v>
+        <v>61.41</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1952,25 +2036,21 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>DyEn</t>
-        </is>
-      </c>
+      <c r="B36" s="1" t="n"/>
       <c r="C36" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3415</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3539374036231884</v>
+        <v>33.44</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3654459192920731</v>
+        <v>29.18</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3309203722854188</v>
+        <v>80.36</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1993,36 +2073,52 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C37" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>42.8</v>
+        <v>50.8</v>
       </c>
       <c r="E37" t="n">
-        <v>43.35</v>
+        <v>36.5</v>
       </c>
       <c r="F37" t="n">
-        <v>41.56</v>
+        <v>36.5</v>
       </c>
       <c r="G37" t="n">
-        <v>46.91</v>
+        <v>0</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="N37" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="R37" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
@@ -2030,30 +2126,26 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>SCL</t>
-        </is>
-      </c>
+      <c r="B38" s="1" t="n"/>
       <c r="C38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.2962962962962963</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.8888888888888888</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="E38" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -2068,55 +2160,51 @@
       <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n"/>
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C39" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>72.5</v>
+        <v>36.25</v>
       </c>
       <c r="E39" t="n">
-        <v>55.8</v>
+        <v>36.7314</v>
       </c>
       <c r="F39" t="n">
-        <v>42.5</v>
+        <v>35.7739</v>
       </c>
       <c r="G39" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="M39" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="N39" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="O39" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="P39" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="R39" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="S39" t="n">
-        <v>38.7</v>
-      </c>
+        <v>38.6464</v>
+      </c>
+      <c r="H39" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="I39" t="n">
+        <v>59.4906</v>
+      </c>
+      <c r="J39" t="n">
+        <v>52.9492</v>
+      </c>
+      <c r="K39" t="n">
+        <v>72.5732</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
@@ -2124,42 +2212,30 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B40" s="1" t="n"/>
       <c r="C40" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>29.85</v>
+        <v>42.35</v>
       </c>
       <c r="E40" t="n">
-        <v>39.2369</v>
+        <v>42.5921</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>39.6705</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>48.4354</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="M40" t="n">
-        <v>47.4674</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -2170,94 +2246,110 @@
       <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>banking</t>
-        </is>
-      </c>
+      <c r="A41" s="1" t="n"/>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C41" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>40.06</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>37.141</v>
+        <v>0.3609324594969105</v>
       </c>
       <c r="F41" t="n">
-        <v>36.5411</v>
+        <v>0.1616352201257861</v>
       </c>
       <c r="G41" t="n">
-        <v>48.5382</v>
-      </c>
-      <c r="H41" t="n">
-        <v>79.29000000000001</v>
-      </c>
-      <c r="I41" t="n">
-        <v>71.46939999999999</v>
-      </c>
-      <c r="J41" t="n">
-        <v>70.7561</v>
-      </c>
-      <c r="K41" t="n">
-        <v>85.02160000000001</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="n">
-        <v>81.04000000000001</v>
-      </c>
-      <c r="U41" t="n">
-        <v>81.5565</v>
-      </c>
-      <c r="V41" t="n">
-        <v>81.5453</v>
-      </c>
-      <c r="W41" t="n">
-        <v>81.9842</v>
-      </c>
+        <v>0.759526938239159</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.1413318782898825</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.0393400783884787</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.6512908777969019</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.2255</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.0884294497836238</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.0568316484109601</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.3412118607649334</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n"/>
-      <c r="B42" s="1" t="n"/>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>DeepUnk</t>
+        </is>
+      </c>
       <c r="C42" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>33.96</v>
+        <v>0.776</v>
       </c>
       <c r="E42" t="n">
-        <v>34.7043</v>
+        <v>0.4685069098477059</v>
       </c>
       <c r="F42" t="n">
-        <v>34.4892</v>
+        <v>0.268814867141227</v>
       </c>
       <c r="G42" t="n">
-        <v>38.7928</v>
+        <v>0.8678909952606635</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>0.5285</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.2194583021384733</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.1279462358580935</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.6770186335403726</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.1841581883731876</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.1632392507886959</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.3515096890491212</v>
+      </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
@@ -2267,40 +2359,32 @@
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C43" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6720779220779221</v>
+        <v>0.3415</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0413217674908714</v>
+        <v>0.3539374036231884</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0006538084341288</v>
+        <v>0.3654459192920731</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8140129895689825</v>
+        <v>0.3309203722854188</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="n">
-        <v>0.4457792207792208</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.017431395836878</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.0009701673538685</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0.6429580781912388</v>
-      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2312,42 +2396,30 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n"/>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>DeepUnk</t>
-        </is>
-      </c>
+      <c r="B44" s="1" t="n"/>
       <c r="C44" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1961038961038961</v>
+        <v>0.282</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3864980042363586</v>
+        <v>0.3279869128126523</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4054625633893641</v>
+        <v>0.3820298469539976</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0261713803292528</v>
+        <v>0.2199010445299615</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="n">
-        <v>0.4048701298701299</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0.4808103046005403</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.4857320149654371</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0.2937853107344633</v>
-      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -2361,40 +2433,32 @@
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C45" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6366883116883116</v>
+        <v>42.8</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6362490626508748</v>
+        <v>43.35</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6332681170383576</v>
+        <v>41.56</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6928870292887029</v>
+        <v>46.91</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="n">
-        <v>0.7084415584415584</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.7796416973694552</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.7828153076170082</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0.6590445079624336</v>
-      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -2411,16 +2475,16 @@
         <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6811688311688312</v>
+        <v>33.9</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6865504160531232</v>
+        <v>39.96</v>
       </c>
       <c r="F46" t="n">
-        <v>0.683705569213898</v>
+        <v>43.71</v>
       </c>
       <c r="G46" t="n">
-        <v>0.7406025059984004</v>
+        <v>32.47</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -2443,40 +2507,40 @@
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C47" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>79.64</v>
+        <v>0.8</v>
       </c>
       <c r="E47" t="n">
-        <v>72.09</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="F47" t="n">
-        <v>71.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>85.20999999999999</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="n">
-        <v>76.75</v>
-      </c>
-      <c r="M47" t="n">
-        <v>80.38</v>
-      </c>
-      <c r="N47" t="n">
-        <v>80.51000000000001</v>
-      </c>
-      <c r="O47" t="n">
-        <v>75.34</v>
-      </c>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.2962962962962963</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -2493,16 +2557,16 @@
         <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>65.52</v>
+        <v>0.8</v>
       </c>
       <c r="E48" t="n">
-        <v>68.37</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="F48" t="n">
-        <v>68.2</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>71.56</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -2525,56 +2589,56 @@
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C49" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.7532467532467533</v>
+        <v>72.5</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0429629629629629</v>
+        <v>55.8</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8592592592592593</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.7532467532467533</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.0429629629629629</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.8592592592592593</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="n">
-        <v>0.7068181818181818</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0.6867082171891119</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0.6852651401605222</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0.7415451442755197</v>
-      </c>
+        <v>82.5</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="M49" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="N49" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="O49" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="P49" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="R49" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="S49" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n"/>
@@ -2583,16 +2647,16 @@
         <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>0.7532467532467533</v>
+        <v>66.8</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0429629629629629</v>
+        <v>56.2</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>45.8</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8592592592592593</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -2615,51 +2679,51 @@
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C51" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>76.40000000000001</v>
+        <v>29.85</v>
       </c>
       <c r="E51" t="n">
-        <v>58.4</v>
+        <v>39.2369</v>
       </c>
       <c r="F51" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>84.8</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
-        <v>67.3</v>
+        <v>41.5</v>
       </c>
       <c r="M51" t="n">
-        <v>61.6</v>
+        <v>47.4674</v>
       </c>
       <c r="N51" t="n">
-        <v>61.3</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>73.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>58.6</v>
+        <v>58.85</v>
       </c>
       <c r="Q51" t="n">
-        <v>61.9</v>
+        <v>59.8367</v>
       </c>
       <c r="R51" t="n">
-        <v>62.1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>50.8</v>
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
@@ -2667,141 +2731,165 @@
       <c r="W51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n"/>
-      <c r="B52" s="1" t="n"/>
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>banking</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
       <c r="C52" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>74.40000000000001</v>
+        <v>40.06</v>
       </c>
       <c r="E52" t="n">
-        <v>57.5</v>
+        <v>37.141</v>
       </c>
       <c r="F52" t="n">
-        <v>56.2</v>
+        <v>36.5411</v>
       </c>
       <c r="G52" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+        <v>48.5382</v>
+      </c>
+      <c r="H52" t="n">
+        <v>79.29000000000001</v>
+      </c>
+      <c r="I52" t="n">
+        <v>71.46939999999999</v>
+      </c>
+      <c r="J52" t="n">
+        <v>70.7561</v>
+      </c>
+      <c r="K52" t="n">
+        <v>85.02160000000001</v>
+      </c>
+      <c r="L52" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="M52" t="n">
+        <v>60.1404</v>
+      </c>
+      <c r="N52" t="n">
+        <v>59.968</v>
+      </c>
+      <c r="O52" t="n">
+        <v>66.6913</v>
+      </c>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
+      <c r="T52" t="n">
+        <v>81.04000000000001</v>
+      </c>
+      <c r="U52" t="n">
+        <v>81.5565</v>
+      </c>
+      <c r="V52" t="n">
+        <v>81.5453</v>
+      </c>
+      <c r="W52" t="n">
+        <v>81.9842</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n"/>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B53" s="1" t="n"/>
       <c r="C53" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>46.75</v>
+        <v>33.96</v>
       </c>
       <c r="E53" t="n">
-        <v>50.2914</v>
+        <v>34.7043</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>34.4892</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>38.7928</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>39.38</v>
+        <v>56.56</v>
       </c>
       <c r="M53" t="n">
-        <v>56.1519</v>
+        <v>55.4223</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>55.3165</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>63.38</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>72.78319999999999</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
+        <v>59.443</v>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>clinc</t>
-        </is>
-      </c>
+      <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C54" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>78</v>
+        <v>0.6720779220779221</v>
       </c>
       <c r="E54" t="n">
-        <v>68.4712</v>
+        <v>0.0413217674908714</v>
       </c>
       <c r="F54" t="n">
-        <v>68.0471</v>
+        <v>0.0006538084341288</v>
       </c>
       <c r="G54" t="n">
-        <v>84.58499999999999</v>
-      </c>
-      <c r="H54" t="n">
-        <v>87.06999999999999</v>
-      </c>
-      <c r="I54" t="n">
-        <v>80.7998</v>
-      </c>
-      <c r="J54" t="n">
-        <v>80.5347</v>
-      </c>
-      <c r="K54" t="n">
-        <v>90.87439999999999</v>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+        <v>0.8140129895689825</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="n">
+        <v>0.4457792207792208</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.017431395836878</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.0009701673538685</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.6429580781912388</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.1461038961038961</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.0063377424232128</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.0005784853743806</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0.3403746512554803</v>
+      </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
@@ -2809,34 +2897,54 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n"/>
-      <c r="B55" s="1" t="n"/>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>DeepUnk</t>
+        </is>
+      </c>
       <c r="C55" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>77.2</v>
+        <v>0.1961038961038961</v>
       </c>
       <c r="E55" t="n">
-        <v>66.76139999999999</v>
+        <v>0.3864980042363586</v>
       </c>
       <c r="F55" t="n">
-        <v>66.3121</v>
+        <v>0.4054625633893641</v>
       </c>
       <c r="G55" t="n">
-        <v>83.8347</v>
+        <v>0.0261713803292528</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+      <c r="L55" t="n">
+        <v>0.4048701298701299</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.4808103046005403</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.4857320149654371</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.2937853107344633</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.4704545454545454</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.4943026366845081</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.4964741047666081</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.3683574879227053</v>
+      </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
@@ -2846,32 +2954,40 @@
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C56" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.6366883116883116</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0219220982579761</v>
+        <v>0.6362490626508748</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>0.6332681170383576</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8549618320610687</v>
+        <v>0.6928870292887029</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
+      <c r="L56" t="n">
+        <v>0.7084415584415584</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.7796416973694552</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.7828153076170082</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.6590445079624336</v>
+      </c>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -2883,34 +2999,38 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n"/>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>DeepUnk</t>
-        </is>
-      </c>
+      <c r="B57" s="1" t="n"/>
       <c r="C57" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2453333333333333</v>
+        <v>0.6811688311688312</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4532367071418627</v>
+        <v>0.6865504160531232</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4633778493517164</v>
+        <v>0.683705569213898</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0678733031674208</v>
+        <v>0.7406025059984004</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="L57" t="n">
+        <v>0.7194805194805195</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.7912161893544616</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.7945223581848464</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.6655817737998373</v>
+      </c>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -2924,39 +3044,39 @@
       <c r="A58" s="1" t="n"/>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C58" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0.8368888888888889</v>
+        <v>79.64</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7864961634000692</v>
+        <v>72.09</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7840369134604483</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8799476611056591</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
-        <v>0.8244444444444444</v>
+        <v>76.75</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8673572235349517</v>
+        <v>80.38</v>
       </c>
       <c r="N58" t="n">
-        <v>0.8682117156927298</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="O58" t="n">
-        <v>0.803270311701584</v>
+        <v>75.34</v>
       </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
@@ -2974,25 +3094,33 @@
         <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>0.8484444444444444</v>
+        <v>65.52</v>
       </c>
       <c r="E59" t="n">
-        <v>0.8055937630884049</v>
+        <v>68.37</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8033846868152448</v>
+        <v>68.2</v>
       </c>
       <c r="G59" t="n">
-        <v>0.889538661468486</v>
+        <v>71.56</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="L59" t="n">
+        <v>80.52</v>
+      </c>
+      <c r="M59" t="n">
+        <v>83.89</v>
+      </c>
+      <c r="N59" t="n">
+        <v>84</v>
+      </c>
+      <c r="O59" t="n">
+        <v>79.87</v>
+      </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -3006,40 +3134,64 @@
       <c r="A60" s="1" t="n"/>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C60" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>86.76000000000001</v>
+        <v>0.7532467532467533</v>
       </c>
       <c r="E60" t="n">
-        <v>82.23999999999999</v>
+        <v>0.0429629629629629</v>
       </c>
       <c r="F60" t="n">
-        <v>82.03</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>90.45999999999999</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+        <v>0.8592592592592593</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.0429629629629629</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.8592592592592593</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.5110389610389611</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.0333456603459571</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.0164745259383775</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.6744487678339819</v>
+      </c>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
+      <c r="T60" t="n">
+        <v>0.7068181818181818</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0.6867082171891119</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0.6852651401605222</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0.7415451442755197</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n"/>
@@ -3048,25 +3200,33 @@
         <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>88.04000000000001</v>
+        <v>0.7532467532467533</v>
       </c>
       <c r="E61" t="n">
-        <v>84.48</v>
+        <v>0.0429629629629629</v>
       </c>
       <c r="F61" t="n">
-        <v>84.3</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>91.41</v>
+        <v>0.8592592592592593</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>0.5064935064935064</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.0172413793103448</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.6724137931034483</v>
+      </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -3087,44 +3247,44 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>82.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>67.7</v>
+        <v>58.4</v>
       </c>
       <c r="F62" t="n">
-        <v>67.09999999999999</v>
+        <v>57</v>
       </c>
       <c r="G62" t="n">
-        <v>88.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>73.3</v>
+        <v>67.3</v>
       </c>
       <c r="M62" t="n">
-        <v>70.3</v>
+        <v>61.6</v>
       </c>
       <c r="N62" t="n">
-        <v>70.2</v>
+        <v>61.3</v>
       </c>
       <c r="O62" t="n">
-        <v>76.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="P62" t="n">
-        <v>68.40000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="Q62" t="n">
-        <v>72.3</v>
+        <v>61.9</v>
       </c>
       <c r="R62" t="n">
-        <v>72.40000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="S62" t="n">
-        <v>59</v>
+        <v>50.8</v>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -3138,25 +3298,33 @@
         <v>3</v>
       </c>
       <c r="D63" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="E63" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="G63" t="n">
         <v>82.90000000000001</v>
-      </c>
-      <c r="E63" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="F63" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="G63" t="n">
-        <v>88.8</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+      <c r="L63" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="M63" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="N63" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="O63" t="n">
+        <v>70.8</v>
+      </c>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -3177,10 +3345,10 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>36.44</v>
+        <v>46.75</v>
       </c>
       <c r="E64" t="n">
-        <v>49.4399</v>
+        <v>50.2914</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3193,10 +3361,10 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
-        <v>53.51</v>
+        <v>39.38</v>
       </c>
       <c r="M64" t="n">
-        <v>71.02160000000001</v>
+        <v>56.1519</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -3205,10 +3373,10 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>74.89</v>
+        <v>63.38</v>
       </c>
       <c r="Q64" t="n">
-        <v>85.5643</v>
+        <v>72.78319999999999</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -3224,7 +3392,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hwu</t>
+          <t>clinc</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
@@ -3236,28 +3404,28 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>67.73</v>
+        <v>78</v>
       </c>
       <c r="E65" t="n">
-        <v>47.2084</v>
+        <v>68.4712</v>
       </c>
       <c r="F65" t="n">
-        <v>45.2056</v>
+        <v>68.0471</v>
       </c>
       <c r="G65" t="n">
-        <v>79.2534</v>
+        <v>84.58499999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>81.40000000000001</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>73.509</v>
+        <v>80.7998</v>
       </c>
       <c r="J65" t="n">
-        <v>72.67610000000001</v>
+        <v>80.5347</v>
       </c>
       <c r="K65" t="n">
-        <v>86.8347</v>
+        <v>90.87439999999999</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
@@ -3279,25 +3447,33 @@
         <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>66.18000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="E66" t="n">
-        <v>51.7591</v>
+        <v>66.76139999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>50.1787</v>
+        <v>66.3121</v>
       </c>
       <c r="G66" t="n">
-        <v>77.0468</v>
+        <v>83.8347</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>70.48999999999999</v>
+      </c>
+      <c r="M66" t="n">
+        <v>70.7239</v>
+      </c>
+      <c r="N66" t="n">
+        <v>70.71510000000001</v>
+      </c>
+      <c r="O66" t="n">
+        <v>71.3852</v>
+      </c>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -3318,29 +3494,45 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0.7529069767441861</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="E67" t="n">
-        <v>0.0505316554482489</v>
+        <v>0.0219220982579761</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.8590381426202321</v>
+        <v>0.8549618320610687</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
+      <c r="L67" t="n">
+        <v>0.6635555555555556</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.4972864818903884</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.4940369729759688</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.740999650471863</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.2533333333333333</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.003577480700433</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.4042553191489361</v>
+      </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
@@ -3357,29 +3549,45 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0.1744186046511628</v>
+        <v>0.2453333333333333</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4553564822398199</v>
+        <v>0.4532367071418627</v>
       </c>
       <c r="F68" t="n">
-        <v>0.4838162623798087</v>
+        <v>0.4633778493517164</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>0.0678733031674208</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>0.4693333333333333</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.594195117360772</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.5980151548230181</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.5831111111111111</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.6329349785950765</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.635149392377884</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0.3849206349206349</v>
+      </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
@@ -3396,25 +3604,33 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7015503875968992</v>
+        <v>0.8368888888888889</v>
       </c>
       <c r="E69" t="n">
-        <v>0.6738222157721238</v>
+        <v>0.7864961634000692</v>
       </c>
       <c r="F69" t="n">
-        <v>0.6680616892812824</v>
+        <v>0.7840369134604483</v>
       </c>
       <c r="G69" t="n">
-        <v>0.765990639625585</v>
+        <v>0.8799476611056591</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+      <c r="L69" t="n">
+        <v>0.8244444444444444</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.8673572235349517</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.8682117156927298</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.803270311701584</v>
+      </c>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -3431,25 +3647,33 @@
         <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>0.6908914728682171</v>
+        <v>0.8484444444444444</v>
       </c>
       <c r="E70" t="n">
-        <v>0.6506487139546074</v>
+        <v>0.8055937630884049</v>
       </c>
       <c r="F70" t="n">
-        <v>0.6439208936478604</v>
+        <v>0.8033846868152448</v>
       </c>
       <c r="G70" t="n">
-        <v>0.7582938388625592</v>
+        <v>0.889538661468486</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="L70" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.8664748504619255</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.8671765355395011</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.8138484696437531</v>
+      </c>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -3470,16 +3694,16 @@
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>81.40000000000001</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>74.45</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>73.68000000000001</v>
+        <v>82.03</v>
       </c>
       <c r="G71" t="n">
-        <v>86.7</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -3505,16 +3729,16 @@
         <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>82.56</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>75.22</v>
+        <v>84.48</v>
       </c>
       <c r="F72" t="n">
-        <v>74.45</v>
+        <v>84.3</v>
       </c>
       <c r="G72" t="n">
-        <v>87.52</v>
+        <v>91.41</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -3537,44 +3761,52 @@
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C73" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0.7529069767441861</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0505316554482489</v>
+        <v>67.7</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>0.8590381426202321</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.7529069767441861</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0.0505316554482489</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0.8590381426202321</v>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M73" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="N73" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="O73" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="P73" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="R73" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="S73" t="n">
+        <v>59</v>
+      </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
@@ -3587,25 +3819,33 @@
         <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>0.7267441860465116</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0495147553971083</v>
+        <v>66.3</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>65.8</v>
       </c>
       <c r="G74" t="n">
-        <v>0.8417508417508418</v>
+        <v>88.8</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="L74" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M74" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="N74" t="n">
+        <v>69</v>
+      </c>
+      <c r="O74" t="n">
+        <v>76.7</v>
+      </c>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
@@ -3619,51 +3859,51 @@
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C75" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>85.90000000000001</v>
+        <v>36.44</v>
       </c>
       <c r="E75" t="n">
-        <v>62.5</v>
+        <v>49.4399</v>
       </c>
       <c r="F75" t="n">
-        <v>60.7</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>92.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="n">
-        <v>78</v>
+        <v>53.51</v>
       </c>
       <c r="M75" t="n">
-        <v>69.3</v>
+        <v>71.02160000000001</v>
       </c>
       <c r="N75" t="n">
-        <v>68.8</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>84.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>67.2</v>
+        <v>74.89</v>
       </c>
       <c r="Q75" t="n">
-        <v>66.59999999999999</v>
+        <v>85.5643</v>
       </c>
       <c r="R75" t="n">
-        <v>66.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>65.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
@@ -3671,27 +3911,43 @@
       <c r="W75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n"/>
-      <c r="B76" s="1" t="n"/>
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>hwu</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
       <c r="C76" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>80.90000000000001</v>
+        <v>67.73</v>
       </c>
       <c r="E76" t="n">
-        <v>57</v>
+        <v>47.2084</v>
       </c>
       <c r="F76" t="n">
-        <v>55.1</v>
+        <v>45.2056</v>
       </c>
       <c r="G76" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+        <v>79.2534</v>
+      </c>
+      <c r="H76" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="I76" t="n">
+        <v>73.509</v>
+      </c>
+      <c r="J76" t="n">
+        <v>72.67610000000001</v>
+      </c>
+      <c r="K76" t="n">
+        <v>86.8347</v>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
@@ -3707,25 +3963,21 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n"/>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B77" s="1" t="n"/>
       <c r="C77" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>20.45</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="E77" t="n">
-        <v>36.1465</v>
+        <v>51.7591</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>50.1787</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>77.0468</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -3745,43 +3997,55 @@
       <c r="W77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="inlineStr">
-        <is>
-          <t>mcid</t>
-        </is>
-      </c>
+      <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C78" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="n">
-        <v>67.37</v>
-      </c>
-      <c r="I78" t="n">
-        <v>69.4192</v>
-      </c>
-      <c r="J78" t="n">
-        <v>68.3593</v>
-      </c>
-      <c r="K78" t="n">
-        <v>73.6585</v>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
+      <c r="D78" t="n">
+        <v>0.7529069767441861</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.0505316554482489</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.8590381426202321</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="n">
+        <v>0.5281007751937985</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.0209450241156011</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.6911857958148383</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.2761627906976744</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0.008832690251499201</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0.4328018223234624</v>
+      </c>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
@@ -3791,36 +4055,52 @@
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C79" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>0.7552870090634441</v>
+        <v>0.1744186046511628</v>
       </c>
       <c r="E79" t="n">
-        <v>0.1721170395869191</v>
+        <v>0.4553564822398199</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>0.4838162623798087</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8605851979345955</v>
+        <v>0</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
+      <c r="L79" t="n">
+        <v>0.4467054263565891</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.5746710012582736</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.5815240981467681</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.3553719008264462</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.4835271317829457</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.5904012685899459</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.6011118308953792</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0.0762942779291553</v>
+      </c>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
@@ -3830,23 +4110,23 @@
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C80" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2779456193353474</v>
+        <v>0.7015503875968992</v>
       </c>
       <c r="E80" t="n">
-        <v>0.3419706628197066</v>
+        <v>0.6738222157721238</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3664072229140722</v>
+        <v>0.6680616892812824</v>
       </c>
       <c r="G80" t="n">
-        <v>0.2442244224422442</v>
+        <v>0.765990639625585</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -3867,25 +4147,21 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n"/>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>DyEn</t>
-        </is>
-      </c>
+      <c r="B81" s="1" t="n"/>
       <c r="C81" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>0.7341389728096677</v>
+        <v>0.6908914728682171</v>
       </c>
       <c r="E81" t="n">
-        <v>0.7266145439925927</v>
+        <v>0.6506487139546074</v>
       </c>
       <c r="F81" t="n">
-        <v>0.7111527953753564</v>
+        <v>0.6439208936478604</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7884615384615384</v>
+        <v>0.7582938388625592</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -3906,21 +4182,25 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n"/>
-      <c r="B82" s="1" t="n"/>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
       <c r="C82" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>0.6012084592145015</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>0.5569695272048214</v>
+        <v>74.45</v>
       </c>
       <c r="F82" t="n">
-        <v>0.5304365079365079</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>0.6631016042780749</v>
+        <v>86.7</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -3941,25 +4221,21 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n"/>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>KnnCon</t>
-        </is>
-      </c>
+      <c r="B83" s="1" t="n"/>
       <c r="C83" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>66.47</v>
+        <v>82.56</v>
       </c>
       <c r="E83" t="n">
-        <v>70.43000000000001</v>
+        <v>75.22</v>
       </c>
       <c r="F83" t="n">
-        <v>70.09</v>
+        <v>74.45</v>
       </c>
       <c r="G83" t="n">
-        <v>71.76000000000001</v>
+        <v>87.52</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -3980,26 +4256,38 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n"/>
-      <c r="B84" s="1" t="n"/>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
       <c r="C84" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>78.25</v>
+        <v>0.7529069767441861</v>
       </c>
       <c r="E84" t="n">
-        <v>71.45999999999999</v>
+        <v>0.0505316554482489</v>
       </c>
       <c r="F84" t="n">
-        <v>68.2</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>84.51000000000001</v>
-      </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+        <v>0.8590381426202321</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.7529069767441861</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.0505316554482489</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.8590381426202321</v>
+      </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
@@ -4015,54 +4303,34 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n"/>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>ab</t>
-        </is>
-      </c>
+      <c r="B85" s="1" t="n"/>
       <c r="C85" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>72.5</v>
+        <v>0.7267441860465116</v>
       </c>
       <c r="E85" t="n">
-        <v>49.5</v>
+        <v>0.0495147553971083</v>
       </c>
       <c r="F85" t="n">
-        <v>41.3</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>82.3</v>
+        <v>0.8417508417508418</v>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="M85" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="N85" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="O85" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="P85" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="R85" t="n">
-        <v>43</v>
-      </c>
-      <c r="S85" t="n">
-        <v>41.8</v>
-      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
@@ -4070,34 +4338,54 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n"/>
-      <c r="B86" s="1" t="n"/>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
       <c r="C86" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>74.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="E86" t="n">
-        <v>46.8</v>
+        <v>62.5</v>
       </c>
       <c r="F86" t="n">
-        <v>37.3</v>
+        <v>60.7</v>
       </c>
       <c r="G86" t="n">
-        <v>84.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
+      <c r="L86" t="n">
+        <v>78</v>
+      </c>
+      <c r="M86" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="N86" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="O86" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="P86" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="R86" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="S86" t="n">
+        <v>65.59999999999999</v>
+      </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
@@ -4105,81 +4393,65 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n"/>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B87" s="1" t="n"/>
       <c r="C87" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D87" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57</v>
+      </c>
+      <c r="F87" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>88.90000000000001</v>
+      </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="n">
-        <v>51.36</v>
-      </c>
-      <c r="M87" t="n">
-        <v>60.1486</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>59.82</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>67.8672</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C88" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="n">
-        <v>72</v>
-      </c>
-      <c r="I88" t="n">
-        <v>66.20140000000001</v>
-      </c>
-      <c r="J88" t="n">
-        <v>63.7654</v>
-      </c>
-      <c r="K88" t="n">
-        <v>78.3813</v>
-      </c>
+      <c r="D88" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="E88" t="n">
+        <v>36.1465</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
@@ -4194,31 +4466,35 @@
       <c r="W88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n"/>
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C89" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D89" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0.1415420023014959</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="n">
-        <v>0.8492520138089759</v>
-      </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="n">
+        <v>67.37</v>
+      </c>
+      <c r="I89" t="n">
+        <v>69.4192</v>
+      </c>
+      <c r="J89" t="n">
+        <v>68.3593</v>
+      </c>
+      <c r="K89" t="n">
+        <v>73.6585</v>
+      </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
@@ -4236,36 +4512,52 @@
       <c r="A90" s="1" t="n"/>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C90" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0.754</v>
+        <v>0.7552870090634441</v>
       </c>
       <c r="E90" t="n">
-        <v>0.2397471839495868</v>
+        <v>0.1721170395869191</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1163012719022949</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.8569767441860465</v>
+        <v>0.8605851979345955</v>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
+      <c r="L90" t="n">
+        <v>0.5075528700906344</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.07481629926519701</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.6733466933867736</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0.256797583081571</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0.0314349112426035</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0.4086538461538461</v>
+      </c>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
@@ -4275,36 +4567,52 @@
       <c r="A91" s="1" t="n"/>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C91" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0.543</v>
+        <v>0.2779456193353474</v>
       </c>
       <c r="E91" t="n">
-        <v>0.5499067233508657</v>
+        <v>0.3419706628197066</v>
       </c>
       <c r="F91" t="n">
-        <v>0.5462604288655685</v>
+        <v>0.3664072229140722</v>
       </c>
       <c r="G91" t="n">
-        <v>0.5681381957773513</v>
+        <v>0.2442244224422442</v>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
+      <c r="L91" t="n">
+        <v>0.3897280966767371</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.4761358567823756</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.5114982495081919</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.1932367149758454</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.5226586102719033</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0.5884257251366416</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0.6374612022313617</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
@@ -4314,23 +4622,23 @@
       <c r="A92" s="1" t="n"/>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DyEn</t>
         </is>
       </c>
       <c r="C92" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>69.84999999999999</v>
+        <v>0.7341389728096677</v>
       </c>
       <c r="E92" t="n">
-        <v>67.54000000000001</v>
+        <v>0.7266145439925927</v>
       </c>
       <c r="F92" t="n">
-        <v>65.97</v>
+        <v>0.7111527953753564</v>
       </c>
       <c r="G92" t="n">
-        <v>75.38</v>
+        <v>0.7884615384615384</v>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -4351,30 +4659,26 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n"/>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>SCL</t>
-        </is>
-      </c>
+      <c r="B93" s="1" t="n"/>
       <c r="C93" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0.1415420023014959</v>
-      </c>
-      <c r="J93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0.8492520138089759</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.6012084592145015</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.5569695272048214</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.5304365079365079</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.6631016042780749</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
@@ -4392,52 +4696,36 @@
       <c r="A94" s="1" t="n"/>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>KnnCon</t>
         </is>
       </c>
       <c r="C94" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>66.7</v>
+        <v>66.47</v>
       </c>
       <c r="E94" t="n">
-        <v>49.3</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="F94" t="n">
-        <v>43.7</v>
+        <v>70.09</v>
       </c>
       <c r="G94" t="n">
-        <v>77.7</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="M94" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="N94" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="O94" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="P94" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="R94" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="S94" t="n">
-        <v>40</v>
-      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
@@ -4445,105 +4733,89 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n"/>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B95" s="1" t="n"/>
       <c r="C95" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>30.8</v>
+        <v>78.25</v>
       </c>
       <c r="E95" t="n">
-        <v>38.4882</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>68.2</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="n">
-        <v>49.65</v>
-      </c>
-      <c r="M95" t="n">
-        <v>59.761</v>
-      </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
-        <v>62.45</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>67.5523</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="n">
-        <v>0</v>
-      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
       <c r="W95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="inlineStr">
-        <is>
-          <t>stackoverflow</t>
-        </is>
-      </c>
+      <c r="A96" s="1" t="n"/>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C96" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>66.15000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="E96" t="n">
-        <v>63.7554</v>
+        <v>49.5</v>
       </c>
       <c r="F96" t="n">
-        <v>61.5881</v>
+        <v>41.3</v>
       </c>
       <c r="G96" t="n">
-        <v>74.59229999999999</v>
-      </c>
-      <c r="H96" t="n">
-        <v>80.79000000000001</v>
-      </c>
-      <c r="I96" t="n">
-        <v>73.0835</v>
-      </c>
-      <c r="J96" t="n">
-        <v>70.32259999999999</v>
-      </c>
-      <c r="K96" t="n">
-        <v>86.88800000000001</v>
-      </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
+        <v>82.3</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="M96" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="N96" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="O96" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="P96" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="R96" t="n">
+        <v>43</v>
+      </c>
+      <c r="S96" t="n">
+        <v>41.8</v>
+      </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
@@ -4556,16 +4828,16 @@
         <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>77.67</v>
+        <v>74.3</v>
       </c>
       <c r="E97" t="n">
-        <v>72.7028</v>
+        <v>46.8</v>
       </c>
       <c r="F97" t="n">
-        <v>70.43940000000001</v>
+        <v>37.3</v>
       </c>
       <c r="G97" t="n">
-        <v>84.01990000000001</v>
+        <v>84.7</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
@@ -4588,67 +4860,87 @@
       <c r="A98" s="1" t="n"/>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C98" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D98" t="n">
-        <v>0.7552996160908029</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0.6125494108169093</v>
-      </c>
-      <c r="F98" t="n">
-        <v>0.5663624416817391</v>
-      </c>
-      <c r="G98" t="n">
-        <v>0.8434842564927603</v>
-      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
+      <c r="L98" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="M98" t="n">
+        <v>60.1486</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>67.8672</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n"/>
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C99" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.7606409614421632</v>
+        <v>47.28</v>
       </c>
       <c r="E99" t="n">
-        <v>0.3466582912392981</v>
+        <v>49.4819</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2444188771679557</v>
+        <v>49.0176</v>
       </c>
       <c r="G99" t="n">
-        <v>0.8578553615960099</v>
-      </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+        <v>51.8033</v>
+      </c>
+      <c r="H99" t="n">
+        <v>72</v>
+      </c>
+      <c r="I99" t="n">
+        <v>66.20140000000001</v>
+      </c>
+      <c r="J99" t="n">
+        <v>63.7654</v>
+      </c>
+      <c r="K99" t="n">
+        <v>78.3813</v>
+      </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
@@ -4664,25 +4956,21 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n"/>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>DyEn</t>
-        </is>
-      </c>
+      <c r="B100" s="1" t="n"/>
       <c r="C100" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4453346686696712</v>
+        <v>35.49</v>
       </c>
       <c r="E100" t="n">
-        <v>0.4807412920773473</v>
+        <v>43.0567</v>
       </c>
       <c r="F100" t="n">
-        <v>0.4862991131948756</v>
+        <v>45.2942</v>
       </c>
       <c r="G100" t="n">
-        <v>0.4529521864897056</v>
+        <v>31.869</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
@@ -4703,34 +4991,54 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n"/>
-      <c r="B101" s="1" t="n"/>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
       <c r="C101" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>0.599899849774662</v>
+        <v>0.738</v>
       </c>
       <c r="E101" t="n">
-        <v>0.6214129244594941</v>
+        <v>0.1415420023014959</v>
       </c>
       <c r="F101" t="n">
-        <v>0.6156925533951411</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.6500147797812592</v>
+        <v>0.8492520138089759</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
+      <c r="L101" t="n">
+        <v>0.5335</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.1907518468249577</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.1420480951153784</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.6777893639207507</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0.0233739837398373</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0.3739837398373983</v>
+      </c>
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
@@ -4740,36 +5048,52 @@
       <c r="A102" s="1" t="n"/>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>KnnCon</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C102" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>58.52</v>
+        <v>0.754</v>
       </c>
       <c r="E102" t="n">
-        <v>57.44</v>
+        <v>0.2397471839495868</v>
       </c>
       <c r="F102" t="n">
-        <v>55.96</v>
+        <v>0.1163012719022949</v>
       </c>
       <c r="G102" t="n">
-        <v>64.84999999999999</v>
+        <v>0.8569767441860465</v>
       </c>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
+      <c r="L102" t="n">
+        <v>0.5245</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.2092355085673985</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.1633289368321943</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.6683012259194396</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0.3057995984319704</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.2997691816451678</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0.3962558502340094</v>
+      </c>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
@@ -4777,21 +5101,25 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n"/>
-      <c r="B103" s="1" t="n"/>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
       <c r="C103" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>73.19</v>
+        <v>0.543</v>
       </c>
       <c r="E103" t="n">
-        <v>70.20999999999999</v>
+        <v>0.5499067233508657</v>
       </c>
       <c r="F103" t="n">
-        <v>68.42</v>
+        <v>0.5462604288655685</v>
       </c>
       <c r="G103" t="n">
-        <v>79.15000000000001</v>
+        <v>0.5681381957773513</v>
       </c>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
@@ -4812,54 +5140,34 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n"/>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>ab</t>
-        </is>
-      </c>
+      <c r="B104" s="1" t="n"/>
       <c r="C104" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>73.7</v>
+        <v>0.5255</v>
       </c>
       <c r="E104" t="n">
-        <v>58.1</v>
+        <v>0.5344507295147621</v>
       </c>
       <c r="F104" t="n">
-        <v>53.1</v>
+        <v>0.5334229868546647</v>
       </c>
       <c r="G104" t="n">
-        <v>83.2</v>
+        <v>0.5395894428152492</v>
       </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="M104" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="N104" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="O104" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="P104" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="R104" t="n">
-        <v>66</v>
-      </c>
-      <c r="S104" t="n">
-        <v>53.5</v>
-      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
@@ -4867,21 +5175,25 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n"/>
-      <c r="B105" s="1" t="n"/>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
       <c r="C105" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>80</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="E105" t="n">
-        <v>65.40000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>61</v>
+        <v>65.97</v>
       </c>
       <c r="G105" t="n">
-        <v>87</v>
+        <v>75.38</v>
       </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
@@ -4902,113 +5214,81 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n"/>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B106" s="1" t="n"/>
       <c r="C106" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>31.11</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E106" t="n">
-        <v>47.2715</v>
+        <v>72.16</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>70.58</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>80.05</v>
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="n">
-        <v>43.97</v>
-      </c>
-      <c r="M106" t="n">
-        <v>59.0736</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="n">
-        <v>80.77</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>84.18899999999999</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="n">
-        <v>0</v>
-      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="inlineStr">
-        <is>
-          <t>thucnews</t>
-        </is>
-      </c>
+      <c r="A107" s="1" t="n"/>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="C107" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>32.7</v>
+        <v>0.738</v>
       </c>
       <c r="E107" t="n">
-        <v>26.7</v>
+        <v>0.1415420023014959</v>
       </c>
       <c r="F107" t="n">
-        <v>22.6</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="M107" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="N107" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="O107" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="P107" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="R107" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="S107" t="n">
-        <v>30</v>
-      </c>
+        <v>0.8492520138089759</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.1415420023014959</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.8492520138089759</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
@@ -5016,108 +5296,860 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n"/>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B108" s="1" t="n"/>
       <c r="C108" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>22.94</v>
+        <v>0.7385</v>
       </c>
       <c r="E108" t="n">
-        <v>32.5598</v>
+        <v>0.1415971623046687</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>0.8495829738280126</v>
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
-      <c r="L108" t="n">
-        <v>35.19</v>
-      </c>
-      <c r="M108" t="n">
-        <v>43.5344</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>50.32</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>54.4698</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" t="n">
-        <v>0</v>
-      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" s="1" t="n"/>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="E109" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="F109" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="G109" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="M109" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="N109" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="O109" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="P109" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="R109" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="S109" t="n">
+        <v>40</v>
+      </c>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n"/>
+      <c r="B110" s="1" t="n"/>
+      <c r="C110" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="E110" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="F110" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="G110" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n"/>
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E111" t="n">
+        <v>38.4882</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="M111" t="n">
+        <v>59.761</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>67.5523</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>66.15000000000001</v>
+      </c>
+      <c r="E112" t="n">
+        <v>63.7554</v>
+      </c>
+      <c r="F112" t="n">
+        <v>61.5881</v>
+      </c>
+      <c r="G112" t="n">
+        <v>74.59229999999999</v>
+      </c>
+      <c r="H112" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="I112" t="n">
+        <v>73.0835</v>
+      </c>
+      <c r="J112" t="n">
+        <v>70.32259999999999</v>
+      </c>
+      <c r="K112" t="n">
+        <v>86.88800000000001</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n"/>
+      <c r="B113" s="1" t="n"/>
+      <c r="C113" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D113" t="n">
+        <v>77.67</v>
+      </c>
+      <c r="E113" t="n">
+        <v>72.7028</v>
+      </c>
+      <c r="F113" t="n">
+        <v>70.43940000000001</v>
+      </c>
+      <c r="G113" t="n">
+        <v>84.01990000000001</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n"/>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.7552996160908029</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.6125494108169093</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.5663624416817391</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.8434842564927603</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="n">
+        <v>0.7347688198965114</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.6875742279523628</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0.6783958153965095</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.7793583535108959</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0.6890335503254882</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0.7203835290749597</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0.727683731719721</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0.6108804894035395</v>
+      </c>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n"/>
+      <c r="B115" s="1" t="inlineStr">
+        <is>
+          <t>DeepUnk</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.7606409614421632</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.3466582912392981</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.2444188771679557</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.8578553615960099</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="n">
+        <v>0.5751961275246202</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.3025259371014686</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.2626832030488756</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.7009532776273979</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0.3994324820564179</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0.3302283193178961</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0.3220567764969455</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0.4528014616321559</v>
+      </c>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n"/>
+      <c r="B116" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.4453346686696712</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.4807412920773473</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.4862991131948756</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.4529521864897056</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n"/>
+      <c r="B117" s="1" t="n"/>
+      <c r="C117" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.599899849774662</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6214129244594941</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.6156925533951411</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.6500147797812592</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n"/>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>58.52</v>
+      </c>
+      <c r="E118" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="F118" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="G118" t="n">
+        <v>64.84999999999999</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n"/>
+      <c r="B119" s="1" t="n"/>
+      <c r="C119" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D119" t="n">
+        <v>73.19</v>
+      </c>
+      <c r="E119" t="n">
+        <v>70.20999999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>68.42</v>
+      </c>
+      <c r="G119" t="n">
+        <v>79.15000000000001</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n"/>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="E120" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="F120" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="G120" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="M120" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="N120" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="O120" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="P120" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="R120" t="n">
+        <v>66</v>
+      </c>
+      <c r="S120" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n"/>
+      <c r="B121" s="1" t="n"/>
+      <c r="C121" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D121" t="n">
+        <v>80</v>
+      </c>
+      <c r="E121" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="F121" t="n">
+        <v>61</v>
+      </c>
+      <c r="G121" t="n">
+        <v>87</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="M121" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="N121" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="O121" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n"/>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="E122" t="n">
+        <v>47.2715</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="M122" t="n">
+        <v>59.0736</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>84.18899999999999</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E123" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F123" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G123" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="M123" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="N123" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="O123" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="P123" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="R123" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="S123" t="n">
+        <v>30</v>
+      </c>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n"/>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="E124" t="n">
+        <v>32.5598</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="n">
+        <v>35.19</v>
+      </c>
+      <c r="M124" t="n">
+        <v>43.5344</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>54.4698</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
+      <c r="W124" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="A17:A26"/>
+  <mergeCells count="64">
     <mergeCell ref="B71:B72"/>
+    <mergeCell ref="B109:B110"/>
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="B62:B63"/>
-    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="B96:B97"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="A41:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="B11:B12"/>
     <mergeCell ref="B73:B74"/>
+    <mergeCell ref="A99:A111"/>
     <mergeCell ref="B58:B59"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A65:A77"/>
-    <mergeCell ref="A88:A95"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="A65:A75"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B116:B117"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="B69:B70"/>
     <mergeCell ref="D1:G1"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="B28:B29"/>
     <mergeCell ref="H1:K1"/>
-    <mergeCell ref="A27:A32"/>
+    <mergeCell ref="A76:A88"/>
+    <mergeCell ref="A112:A122"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="A5:A17"/>
+    <mergeCell ref="B84:B85"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="A78:A87"/>
+    <mergeCell ref="B80:B81"/>
     <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B118:B119"/>
     <mergeCell ref="B65:B66"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="A96:A106"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="B33:B34"/>
     <mergeCell ref="L1:S1"/>
-    <mergeCell ref="A33:A40"/>
+    <mergeCell ref="B99:B100"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="P2:S2"/>
+    <mergeCell ref="A89:A98"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="B76:B77"/>
     <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="A30:A38"/>
+    <mergeCell ref="A52:A64"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A39:A51"/>
     <mergeCell ref="H2:K2"/>
+    <mergeCell ref="B56:B57"/>
     <mergeCell ref="T2:W2"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="A107:A108"/>
-    <mergeCell ref="A54:A64"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A5:A16"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="A18:A29"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="B35:B36"/>
     <mergeCell ref="T1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/openset_pivot.xlsx
+++ b/results/openset_pivot.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W124"/>
+  <dimension ref="A1:W125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,19 +489,19 @@
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="n"/>
       <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
+      <c r="P1" s="1" t="n">
+        <v>0.1</v>
+      </c>
       <c r="Q1" s="1" t="n"/>
       <c r="R1" s="1" t="n"/>
       <c r="S1" s="1" t="n"/>
@@ -525,13 +525,13 @@
       <c r="F2" s="1" t="n"/>
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I2" s="1" t="n"/>
       <c r="J2" s="1" t="n"/>
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="M2" s="1" t="n"/>
       <c r="N2" s="1" t="n"/>
@@ -700,21 +700,29 @@
         <v>62.515</v>
       </c>
       <c r="H5" t="n">
+        <v>60.39</v>
+      </c>
+      <c r="I5" t="n">
+        <v>69.627</v>
+      </c>
+      <c r="J5" t="n">
+        <v>71.6784</v>
+      </c>
+      <c r="K5" t="n">
+        <v>49.113</v>
+      </c>
+      <c r="L5" t="n">
         <v>64.69</v>
       </c>
-      <c r="I5" t="n">
+      <c r="M5" t="n">
         <v>67.9614</v>
       </c>
-      <c r="J5" t="n">
+      <c r="N5" t="n">
         <v>67.5778</v>
       </c>
-      <c r="K5" t="n">
+      <c r="O5" t="n">
         <v>69.87949999999999</v>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -742,10 +750,18 @@
       <c r="G6" t="n">
         <v>53.821</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>62.88</v>
+      </c>
+      <c r="I6" t="n">
+        <v>69.5776</v>
+      </c>
+      <c r="J6" t="n">
+        <v>71.07899999999999</v>
+      </c>
+      <c r="K6" t="n">
+        <v>54.5631</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -781,22 +797,22 @@
       <c r="G7" t="n">
         <v>0.8729314420803782</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
+      <c r="H7" t="n">
         <v>0.5625</v>
       </c>
-      <c r="M7" t="n">
+      <c r="I7" t="n">
         <v>0.2310855173976649</v>
       </c>
-      <c r="N7" t="n">
+      <c r="J7" t="n">
         <v>0.1846500385074279</v>
       </c>
-      <c r="O7" t="n">
+      <c r="K7" t="n">
         <v>0.6954403063000348</v>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>0.445</v>
       </c>
@@ -836,22 +852,22 @@
       <c r="G8" t="n">
         <v>0.8845693779904307</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
+      <c r="H8" t="n">
         <v>0.5885</v>
       </c>
-      <c r="M8" t="n">
+      <c r="I8" t="n">
         <v>0.3303673802612091</v>
       </c>
-      <c r="N8" t="n">
+      <c r="J8" t="n">
         <v>0.292578170042027</v>
       </c>
-      <c r="O8" t="n">
+      <c r="K8" t="n">
         <v>0.7082594824530308</v>
       </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>0.5365</v>
       </c>
@@ -891,10 +907,18 @@
       <c r="G9" t="n">
         <v>0.9939516129032258</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0.9775</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9767498345121546</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9766274611351764</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.9779735682819384</v>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -926,10 +950,18 @@
       <c r="G10" t="n">
         <v>0.9828916470982892</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9918899170241487</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9918886253257538</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9919028340080972</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -965,10 +997,18 @@
       <c r="G11" t="n">
         <v>96.79000000000001</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="J11" t="n">
+        <v>94.91</v>
+      </c>
+      <c r="K11" t="n">
+        <v>94.06999999999999</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1000,10 +1040,18 @@
       <c r="G12" t="n">
         <v>94.27</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="I12" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="J12" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="K12" t="n">
+        <v>99.95</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1040,21 +1088,29 @@
         <v>0.9989868287740628</v>
       </c>
       <c r="H13" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9985461814547272</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9985507246376812</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.9985007496251874</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -1082,10 +1138,18 @@
       <c r="G14" t="n">
         <v>0.9950314673733024</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9938136691069288</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.9938035552873988</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.9939148073022313</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -1121,22 +1185,22 @@
       <c r="G15" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
+      <c r="H15" t="n">
         <v>59.2</v>
       </c>
-      <c r="M15" t="n">
+      <c r="I15" t="n">
         <v>54.9</v>
       </c>
-      <c r="N15" t="n">
+      <c r="J15" t="n">
         <v>53.8</v>
       </c>
-      <c r="O15" t="n">
+      <c r="K15" t="n">
         <v>65</v>
       </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>54.4</v>
       </c>
@@ -1172,10 +1236,18 @@
       <c r="G16" t="n">
         <v>80.5</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>61.5</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -1211,22 +1283,22 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
+      <c r="H17" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="M17" t="n">
+      <c r="I17" t="n">
         <v>86.2758</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>89.45</v>
       </c>
@@ -1271,21 +1343,29 @@
         <v>61.5156</v>
       </c>
       <c r="H18" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>72.6767</v>
+      </c>
+      <c r="J18" t="n">
+        <v>72.7364</v>
+      </c>
+      <c r="K18" t="n">
+        <v>66.1046</v>
+      </c>
+      <c r="L18" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="I18" t="n">
+      <c r="M18" t="n">
         <v>82.6465</v>
       </c>
-      <c r="J18" t="n">
+      <c r="N18" t="n">
         <v>82.6126</v>
       </c>
-      <c r="K18" t="n">
+      <c r="O18" t="n">
         <v>84.5119</v>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -1313,10 +1393,18 @@
       <c r="G19" t="n">
         <v>73.5273</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="I19" t="n">
+        <v>48.2066</v>
+      </c>
+      <c r="J19" t="n">
+        <v>47.9855</v>
+      </c>
+      <c r="K19" t="n">
+        <v>72.5244</v>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -1352,22 +1440,22 @@
       <c r="G20" t="n">
         <v>0.7926350739511017</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
+      <c r="H20" t="n">
         <v>0.3395</v>
       </c>
-      <c r="M20" t="n">
+      <c r="I20" t="n">
         <v>0.0045667167727638</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.5069055617767824</v>
       </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>0.113</v>
       </c>
@@ -1407,22 +1495,22 @@
       <c r="G21" t="n">
         <v>0.1535326086956521</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
+      <c r="H21" t="n">
         <v>0.302</v>
       </c>
-      <c r="M21" t="n">
+      <c r="I21" t="n">
         <v>0.2807982583591505</v>
       </c>
-      <c r="N21" t="n">
+      <c r="J21" t="n">
         <v>0.2824583223945039</v>
       </c>
-      <c r="O21" t="n">
+      <c r="K21" t="n">
         <v>0.0981912144702842</v>
       </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>0.3305</v>
       </c>
@@ -1462,10 +1550,18 @@
       <c r="G22" t="n">
         <v>0.7226970560303894</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0.7965</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8644192406684057</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.8662888780918678</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.6587591240875912</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -1497,10 +1593,18 @@
       <c r="G23" t="n">
         <v>0.7784786641929499</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>0.7075</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7458209578980832</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.7460652007120111</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.7189542483660131</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -1571,10 +1675,18 @@
       <c r="G25" t="n">
         <v>79.25</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>75.65000000000001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="J25" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="K25" t="n">
+        <v>79.34</v>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -1611,21 +1723,29 @@
         <v>0.7940731781070457</v>
       </c>
       <c r="H26" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.0045667167727638</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.5069055617767824</v>
+      </c>
+      <c r="L26" t="n">
         <v>0.7445000000000001</v>
       </c>
-      <c r="I26" t="n">
+      <c r="M26" t="n">
         <v>0.563541059873655</v>
       </c>
-      <c r="J26" t="n">
+      <c r="N26" t="n">
         <v>0.5590021957840905</v>
       </c>
-      <c r="K26" t="n">
+      <c r="O26" t="n">
         <v>0.8131785847997005</v>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -1653,10 +1773,18 @@
       <c r="G27" t="n">
         <v>0.8956377691882937</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.0168395425384359</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.0100056805939158</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.7685643564356436</v>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -1692,22 +1820,22 @@
       <c r="G28" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
+      <c r="H28" t="n">
         <v>49.2</v>
       </c>
-      <c r="M28" t="n">
+      <c r="I28" t="n">
         <v>29.8</v>
       </c>
-      <c r="N28" t="n">
+      <c r="J28" t="n">
         <v>29.5</v>
       </c>
-      <c r="O28" t="n">
+      <c r="K28" t="n">
         <v>56.4</v>
       </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
         <v>33.7</v>
       </c>
@@ -1743,10 +1871,18 @@
       <c r="G29" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I29" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>78.59999999999999</v>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -1787,21 +1923,29 @@
         <v>39.0438</v>
       </c>
       <c r="H30" t="n">
+        <v>62.86</v>
+      </c>
+      <c r="I30" t="n">
+        <v>40.0036</v>
+      </c>
+      <c r="J30" t="n">
+        <v>39.7042</v>
+      </c>
+      <c r="K30" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="L30" t="n">
         <v>80.41</v>
       </c>
-      <c r="I30" t="n">
+      <c r="M30" t="n">
         <v>83.67140000000001</v>
       </c>
-      <c r="J30" t="n">
+      <c r="N30" t="n">
         <v>85.21259999999999</v>
       </c>
-      <c r="K30" t="n">
+      <c r="O30" t="n">
         <v>68.2594</v>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -1813,54 +1957,34 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
+      <c r="B31" s="1" t="n"/>
       <c r="C31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.6775510204081633</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.3748318533937143</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.3486334466932848</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.6368159203980099</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
-        <v>0.1591836734693877</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.0119412124923453</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0.2746478873239437</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0.5612244897959183</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.2529310838927908</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.252249051951459</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0.2740740740740741</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="I31" t="n">
+        <v>17.9373</v>
+      </c>
+      <c r="J31" t="n">
+        <v>17.528</v>
+      </c>
+      <c r="K31" t="n">
+        <v>26.943</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
@@ -1870,51 +1994,51 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4693877551020408</v>
+        <v>0.6775510204081633</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2850229038482891</v>
+        <v>0.3748318533937143</v>
       </c>
       <c r="F32" t="n">
-        <v>0.26323272884383</v>
+        <v>0.3486334466932848</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5247148288973384</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
-        <v>0.4653061224489795</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.3065925054437858</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.3044206160716554</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.3565459610027855</v>
-      </c>
+        <v>0.6368159203980099</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1591836734693877</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.0119412124923453</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.2746478873239437</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5612244897959183</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.1792102670353817</v>
+        <v>0.2529310838927908</v>
       </c>
       <c r="R32" t="n">
-        <v>0.1789512128802374</v>
+        <v>0.252249051951459</v>
       </c>
       <c r="S32" t="n">
-        <v>0.1875</v>
+        <v>0.2740740740740741</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -1925,36 +2049,52 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7122448979591837</v>
+        <v>0.4693877551020408</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6866140378665598</v>
+        <v>0.2850229038482891</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7216630168710466</v>
+        <v>0.26323272884383</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3010752688172043</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+        <v>0.5247148288973384</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4653061224489795</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.3065925054437858</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.3044206160716554</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.3565459610027855</v>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.1792102670353817</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.1789512128802374</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.1875</v>
+      </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
@@ -1962,26 +2102,38 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="1" t="n"/>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
       <c r="C34" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.8020408163265306</v>
+        <v>0.7122448979591837</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3849081787305231</v>
+        <v>0.6866140378665598</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3434723171565277</v>
+        <v>0.7216630168710466</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8821385176184691</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+        <v>0.3010752688172043</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8101224229751445</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.8245350292509126</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.4786324786324786</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -1997,30 +2149,34 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n"/>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>KnnCon</t>
-        </is>
-      </c>
+      <c r="B35" s="1" t="n"/>
       <c r="C35" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>80.2</v>
+        <v>0.8020408163265306</v>
       </c>
       <c r="E35" t="n">
-        <v>84.87</v>
+        <v>0.3849081787305231</v>
       </c>
       <c r="F35" t="n">
-        <v>87.22</v>
+        <v>0.3434723171565277</v>
       </c>
       <c r="G35" t="n">
-        <v>61.41</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+        <v>0.8821385176184691</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.5243354916902583</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.5080574012014455</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.8336192109777015</v>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -2036,21 +2192,25 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="1" t="n"/>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
       <c r="C36" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>69.18000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="E36" t="n">
-        <v>33.44</v>
+        <v>84.87</v>
       </c>
       <c r="F36" t="n">
-        <v>29.18</v>
+        <v>87.22</v>
       </c>
       <c r="G36" t="n">
-        <v>80.36</v>
+        <v>61.41</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2071,54 +2231,42 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>ab</t>
-        </is>
-      </c>
+      <c r="B37" s="1" t="n"/>
       <c r="C37" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>50.8</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>36.5</v>
+        <v>33.44</v>
       </c>
       <c r="F37" t="n">
-        <v>36.5</v>
+        <v>29.18</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="M37" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="N37" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="R37" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
+        <v>80.36</v>
+      </c>
+      <c r="H37" t="n">
+        <v>73.27</v>
+      </c>
+      <c r="I37" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>39.84</v>
+      </c>
+      <c r="K37" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
@@ -2126,76 +2274,88 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="1" t="n"/>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
       <c r="C38" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>89.40000000000001</v>
+        <v>50.8</v>
       </c>
       <c r="E38" t="n">
-        <v>13.6</v>
+        <v>36.5</v>
       </c>
       <c r="F38" t="n">
-        <v>13.6</v>
+        <v>36.5</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="J38" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="R38" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>Yahoo</t>
-        </is>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>ADB</t>
-        </is>
-      </c>
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="1" t="n"/>
       <c r="C39" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>36.25</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>36.7314</v>
+        <v>13.6</v>
       </c>
       <c r="F39" t="n">
-        <v>35.7739</v>
+        <v>13.6</v>
       </c>
       <c r="G39" t="n">
-        <v>38.6464</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>64.09999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="I39" t="n">
-        <v>59.4906</v>
+        <v>14.3</v>
       </c>
       <c r="J39" t="n">
-        <v>52.9492</v>
+        <v>14.3</v>
       </c>
       <c r="K39" t="n">
-        <v>72.5732</v>
+        <v>0</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
@@ -2211,31 +2371,47 @@
       <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n"/>
-      <c r="B40" s="1" t="n"/>
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
       <c r="C40" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>42.35</v>
+        <v>36.25</v>
       </c>
       <c r="E40" t="n">
-        <v>42.5921</v>
+        <v>36.7314</v>
       </c>
       <c r="F40" t="n">
-        <v>39.6705</v>
+        <v>35.7739</v>
       </c>
       <c r="G40" t="n">
-        <v>48.4354</v>
+        <v>38.6464</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="M40" t="n">
+        <v>59.4906</v>
+      </c>
+      <c r="N40" t="n">
+        <v>52.9492</v>
+      </c>
+      <c r="O40" t="n">
+        <v>72.5732</v>
+      </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -2247,54 +2423,42 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
+      <c r="B41" s="1" t="n"/>
       <c r="C41" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6215000000000001</v>
+        <v>42.35</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3609324594969105</v>
+        <v>42.5921</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1616352201257861</v>
+        <v>39.6705</v>
       </c>
       <c r="G41" t="n">
-        <v>0.759526938239159</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.1413318782898825</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0.0393400783884787</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0.6512908777969019</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0.2255</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0.0884294497836238</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.0568316484109601</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0.3412118607649334</v>
-      </c>
+        <v>48.4354</v>
+      </c>
+      <c r="H41" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>51.2638</v>
+      </c>
+      <c r="J41" t="n">
+        <v>54.3377</v>
+      </c>
+      <c r="K41" t="n">
+        <v>35.8939</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
@@ -2304,51 +2468,51 @@
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C42" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.776</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4685069098477059</v>
+        <v>0.3609324594969105</v>
       </c>
       <c r="F42" t="n">
-        <v>0.268814867141227</v>
+        <v>0.1616352201257861</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8678909952606635</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="n">
-        <v>0.5285</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.2194583021384733</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.1279462358580935</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0.6770186335403726</v>
-      </c>
+        <v>0.759526938239159</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.1413318782898825</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.0393400783884787</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.6512908777969019</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>0.271</v>
+        <v>0.2255</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.1841581883731876</v>
+        <v>0.0884294497836238</v>
       </c>
       <c r="R42" t="n">
-        <v>0.1632392507886959</v>
+        <v>0.0568316484109601</v>
       </c>
       <c r="S42" t="n">
-        <v>0.3515096890491212</v>
+        <v>0.3412118607649334</v>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
@@ -2359,36 +2523,52 @@
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C43" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3415</v>
+        <v>0.776</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3539374036231884</v>
+        <v>0.4685069098477059</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3654459192920731</v>
+        <v>0.268814867141227</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3309203722854188</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+        <v>0.8678909952606635</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5285</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.2194583021384733</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.1279462358580935</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.6770186335403726</v>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.1841581883731876</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.1632392507886959</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.3515096890491212</v>
+      </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
@@ -2396,21 +2576,25 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n"/>
-      <c r="B44" s="1" t="n"/>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
       <c r="C44" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.282</v>
+        <v>0.3415</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3279869128126523</v>
+        <v>0.3539374036231884</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3820298469539976</v>
+        <v>0.3654459192920731</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2199010445299615</v>
+        <v>0.3309203722854188</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -2431,30 +2615,34 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n"/>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>KnnCon</t>
-        </is>
-      </c>
+      <c r="B45" s="1" t="n"/>
       <c r="C45" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>42.8</v>
+        <v>0.282</v>
       </c>
       <c r="E45" t="n">
-        <v>43.35</v>
+        <v>0.3279869128126523</v>
       </c>
       <c r="F45" t="n">
-        <v>41.56</v>
+        <v>0.3820298469539976</v>
       </c>
       <c r="G45" t="n">
-        <v>46.91</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+        <v>0.2199010445299615</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.4751762356871872</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.544671914479301</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.1276978417266187</v>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -2470,21 +2658,25 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n"/>
-      <c r="B46" s="1" t="n"/>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
       <c r="C46" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>33.9</v>
+        <v>42.8</v>
       </c>
       <c r="E46" t="n">
-        <v>39.96</v>
+        <v>43.35</v>
       </c>
       <c r="F46" t="n">
-        <v>43.71</v>
+        <v>41.56</v>
       </c>
       <c r="G46" t="n">
-        <v>32.47</v>
+        <v>46.91</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -2505,38 +2697,26 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n"/>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>SCL</t>
-        </is>
-      </c>
+      <c r="B47" s="1" t="n"/>
       <c r="C47" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>0.8</v>
+        <v>33.9</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2962962962962963</v>
+        <v>39.96</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>43.71</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.2962962962962963</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0.8888888888888888</v>
-      </c>
+        <v>32.47</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -2552,9 +2732,13 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n"/>
-      <c r="B48" s="1" t="n"/>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
       <c r="C48" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0.8</v>
@@ -2572,10 +2756,18 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.2962962962962963</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.8888888888888888</v>
+      </c>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -2587,54 +2779,42 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n"/>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>ab</t>
-        </is>
-      </c>
+      <c r="B49" s="1" t="n"/>
       <c r="C49" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>72.5</v>
+        <v>0.8</v>
       </c>
       <c r="E49" t="n">
-        <v>55.8</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="F49" t="n">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="M49" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="N49" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="O49" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="P49" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="R49" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="S49" t="n">
-        <v>38.7</v>
-      </c>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
@@ -2642,34 +2822,54 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n"/>
-      <c r="B50" s="1" t="n"/>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
       <c r="C50" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>66.8</v>
+        <v>72.5</v>
       </c>
       <c r="E50" t="n">
-        <v>56.2</v>
+        <v>55.8</v>
       </c>
       <c r="F50" t="n">
-        <v>45.8</v>
+        <v>42.5</v>
       </c>
       <c r="G50" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+        <v>82.5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="I50" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="J50" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="K50" t="n">
+        <v>57.2</v>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="R50" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="S50" t="n">
+        <v>38.7</v>
+      </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
@@ -2677,219 +2877,207 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n"/>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B51" s="1" t="n"/>
       <c r="C51" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>29.85</v>
+        <v>66.8</v>
       </c>
       <c r="E51" t="n">
-        <v>39.2369</v>
+        <v>56.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>45.8</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="M51" t="n">
-        <v>47.4674</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>58.85</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>59.8367</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>46</v>
+      </c>
+      <c r="K51" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" s="1" t="n"/>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="E52" t="n">
+        <v>39.2369</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="I52" t="n">
+        <v>47.4674</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>58.85</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>59.8367</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
         <is>
           <t>banking</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
+      <c r="B53" s="1" t="inlineStr">
         <is>
           <t>ADB</t>
         </is>
       </c>
-      <c r="C52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="n">
+      <c r="C53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
         <v>40.06</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E53" t="n">
         <v>37.141</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F53" t="n">
         <v>36.5411</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G53" t="n">
         <v>48.5382</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H53" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="I53" t="n">
+        <v>60.1404</v>
+      </c>
+      <c r="J53" t="n">
+        <v>59.968</v>
+      </c>
+      <c r="K53" t="n">
+        <v>66.6913</v>
+      </c>
+      <c r="L53" t="n">
         <v>79.29000000000001</v>
       </c>
-      <c r="I52" t="n">
+      <c r="M53" t="n">
         <v>71.46939999999999</v>
       </c>
-      <c r="J52" t="n">
+      <c r="N53" t="n">
         <v>70.7561</v>
       </c>
-      <c r="K52" t="n">
+      <c r="O53" t="n">
         <v>85.02160000000001</v>
-      </c>
-      <c r="L52" t="n">
-        <v>61.75</v>
-      </c>
-      <c r="M52" t="n">
-        <v>60.1404</v>
-      </c>
-      <c r="N52" t="n">
-        <v>59.968</v>
-      </c>
-      <c r="O52" t="n">
-        <v>66.6913</v>
-      </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="n">
-        <v>81.04000000000001</v>
-      </c>
-      <c r="U52" t="n">
-        <v>81.5565</v>
-      </c>
-      <c r="V52" t="n">
-        <v>81.5453</v>
-      </c>
-      <c r="W52" t="n">
-        <v>81.9842</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n"/>
-      <c r="B53" s="1" t="n"/>
-      <c r="C53" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="D53" t="n">
-        <v>33.96</v>
-      </c>
-      <c r="E53" t="n">
-        <v>34.7043</v>
-      </c>
-      <c r="F53" t="n">
-        <v>34.4892</v>
-      </c>
-      <c r="G53" t="n">
-        <v>38.7928</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="n">
-        <v>56.56</v>
-      </c>
-      <c r="M53" t="n">
-        <v>55.4223</v>
-      </c>
-      <c r="N53" t="n">
-        <v>55.3165</v>
-      </c>
-      <c r="O53" t="n">
-        <v>59.443</v>
       </c>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
+      <c r="T53" t="n">
+        <v>81.04000000000001</v>
+      </c>
+      <c r="U53" t="n">
+        <v>81.5565</v>
+      </c>
+      <c r="V53" t="n">
+        <v>81.5453</v>
+      </c>
+      <c r="W53" t="n">
+        <v>81.9842</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n"/>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
+      <c r="B54" s="1" t="n"/>
       <c r="C54" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>0.6720779220779221</v>
+        <v>33.96</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0413217674908714</v>
+        <v>34.7043</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0006538084341288</v>
+        <v>34.4892</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8140129895689825</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="n">
-        <v>0.4457792207792208</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.017431395836878</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0.0009701673538685</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0.6429580781912388</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0.1461038961038961</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0.0063377424232128</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0.0005784853743806</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0.3403746512554803</v>
-      </c>
+        <v>38.7928</v>
+      </c>
+      <c r="H54" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="I54" t="n">
+        <v>55.4223</v>
+      </c>
+      <c r="J54" t="n">
+        <v>55.3165</v>
+      </c>
+      <c r="K54" t="n">
+        <v>59.443</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
@@ -2899,51 +3087,51 @@
       <c r="A55" s="1" t="n"/>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C55" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0.1961038961038961</v>
+        <v>0.6720779220779221</v>
       </c>
       <c r="E55" t="n">
-        <v>0.3864980042363586</v>
+        <v>0.0413217674908714</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4054625633893641</v>
+        <v>0.0006538084341288</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0261713803292528</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="n">
-        <v>0.4048701298701299</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0.4808103046005403</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0.4857320149654371</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0.2937853107344633</v>
-      </c>
+        <v>0.8140129895689825</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.4457792207792208</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.017431395836878</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.0009701673538685</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.6429580781912388</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>0.4704545454545454</v>
+        <v>0.1461038961038961</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.4943026366845081</v>
+        <v>0.0063377424232128</v>
       </c>
       <c r="R55" t="n">
-        <v>0.4964741047666081</v>
+        <v>0.0005784853743806</v>
       </c>
       <c r="S55" t="n">
-        <v>0.3683574879227053</v>
+        <v>0.3403746512554803</v>
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
@@ -2954,44 +3142,52 @@
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C56" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0.6366883116883116</v>
+        <v>0.1961038961038961</v>
       </c>
       <c r="E56" t="n">
-        <v>0.6362490626508748</v>
+        <v>0.3864980042363586</v>
       </c>
       <c r="F56" t="n">
-        <v>0.6332681170383576</v>
+        <v>0.4054625633893641</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6928870292887029</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="n">
-        <v>0.7084415584415584</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.7796416973694552</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.7828153076170082</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0.6590445079624336</v>
-      </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
+        <v>0.0261713803292528</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.4048701298701299</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.4808103046005403</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.4857320149654371</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.2937853107344633</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>0.4704545454545454</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.4943026366845081</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.4964741047666081</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.3683574879227053</v>
+      </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
@@ -2999,38 +3195,42 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n"/>
-      <c r="B57" s="1" t="n"/>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
       <c r="C57" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>0.6811688311688312</v>
+        <v>0.6366883116883116</v>
       </c>
       <c r="E57" t="n">
-        <v>0.6865504160531232</v>
+        <v>0.6362490626508748</v>
       </c>
       <c r="F57" t="n">
-        <v>0.683705569213898</v>
+        <v>0.6332681170383576</v>
       </c>
       <c r="G57" t="n">
-        <v>0.7406025059984004</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="n">
-        <v>0.7194805194805195</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.7912161893544616</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0.7945223581848464</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0.6655817737998373</v>
-      </c>
+        <v>0.6928870292887029</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.7084415584415584</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.7796416973694552</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.7828153076170082</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.6590445079624336</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3042,42 +3242,38 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n"/>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>KnnCon</t>
-        </is>
-      </c>
+      <c r="B58" s="1" t="n"/>
       <c r="C58" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>79.64</v>
+        <v>0.6811688311688312</v>
       </c>
       <c r="E58" t="n">
-        <v>72.09</v>
+        <v>0.6865504160531232</v>
       </c>
       <c r="F58" t="n">
-        <v>71.40000000000001</v>
+        <v>0.683705569213898</v>
       </c>
       <c r="G58" t="n">
-        <v>85.20999999999999</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="n">
-        <v>76.75</v>
-      </c>
-      <c r="M58" t="n">
-        <v>80.38</v>
-      </c>
-      <c r="N58" t="n">
-        <v>80.51000000000001</v>
-      </c>
-      <c r="O58" t="n">
-        <v>75.34</v>
-      </c>
+        <v>0.7406025059984004</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.7194805194805195</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.7912161893544616</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.7945223581848464</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.6655817737998373</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -3089,38 +3285,42 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n"/>
-      <c r="B59" s="1" t="n"/>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
       <c r="C59" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>65.52</v>
+        <v>79.64</v>
       </c>
       <c r="E59" t="n">
-        <v>68.37</v>
+        <v>72.09</v>
       </c>
       <c r="F59" t="n">
-        <v>68.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>71.56</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="n">
-        <v>80.52</v>
-      </c>
-      <c r="M59" t="n">
-        <v>83.89</v>
-      </c>
-      <c r="N59" t="n">
-        <v>84</v>
-      </c>
-      <c r="O59" t="n">
-        <v>79.87</v>
-      </c>
+        <v>85.20999999999999</v>
+      </c>
+      <c r="H59" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="I59" t="n">
+        <v>80.38</v>
+      </c>
+      <c r="J59" t="n">
+        <v>80.51000000000001</v>
+      </c>
+      <c r="K59" t="n">
+        <v>75.34</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -3132,72 +3332,56 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n"/>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>SCL</t>
-        </is>
-      </c>
+      <c r="B60" s="1" t="n"/>
       <c r="C60" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>0.7532467532467533</v>
+        <v>65.52</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0429629629629629</v>
+        <v>68.37</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>68.2</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8592592592592593</v>
+        <v>71.56</v>
       </c>
       <c r="H60" t="n">
-        <v>0.7532467532467533</v>
+        <v>80.52</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0429629629629629</v>
+        <v>83.89</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="K60" t="n">
-        <v>0.8592592592592593</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0.5110389610389611</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0.0333456603459571</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0.0164745259383775</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0.6744487678339819</v>
-      </c>
+        <v>79.87</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
-      <c r="T60" t="n">
-        <v>0.7068181818181818</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0.6867082171891119</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0.6852651401605222</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0.7415451442755197</v>
-      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n"/>
-      <c r="B61" s="1" t="n"/>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
       <c r="C61" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
         <v>0.7532467532467533</v>
@@ -3211,81 +3395,85 @@
       <c r="G61" t="n">
         <v>0.8592592592592593</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>0.5110389610389611</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.0333456603459571</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.0164745259383775</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.6744487678339819</v>
+      </c>
       <c r="L61" t="n">
-        <v>0.5064935064935064</v>
+        <v>0.7532467532467533</v>
       </c>
       <c r="M61" t="n">
-        <v>0.0172413793103448</v>
+        <v>0.0429629629629629</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0.6724137931034483</v>
+        <v>0.8592592592592593</v>
       </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
+      <c r="T61" t="n">
+        <v>0.7068181818181818</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0.6867082171891119</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0.6852651401605222</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0.7415451442755197</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n"/>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>ab</t>
-        </is>
-      </c>
+      <c r="B62" s="1" t="n"/>
       <c r="C62" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>76.40000000000001</v>
+        <v>0.7532467532467533</v>
       </c>
       <c r="E62" t="n">
-        <v>58.4</v>
+        <v>0.0429629629629629</v>
       </c>
       <c r="F62" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="M62" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="N62" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="O62" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="P62" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="R62" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="S62" t="n">
-        <v>50.8</v>
-      </c>
+        <v>0.8592592592592593</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.5064935064935064</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.0172413793103448</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.6724137931034483</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
@@ -3293,42 +3481,54 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n"/>
-      <c r="B63" s="1" t="n"/>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
       <c r="C63" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>74.40000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>57.5</v>
+        <v>58.4</v>
       </c>
       <c r="F63" t="n">
-        <v>56.2</v>
+        <v>57</v>
       </c>
       <c r="G63" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="M63" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="N63" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="O63" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+        <v>84.8</v>
+      </c>
+      <c r="H63" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="I63" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="J63" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="K63" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="R63" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="S63" t="n">
+        <v>50.8</v>
+      </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
@@ -3336,53 +3536,49 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n"/>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B64" s="1" t="n"/>
       <c r="C64" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>46.75</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>50.2914</v>
+        <v>57.5</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>56.2</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="n">
-        <v>39.38</v>
-      </c>
-      <c r="M64" t="n">
-        <v>56.1519</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
+        <v>82.90000000000001</v>
+      </c>
+      <c r="H64" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="I64" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="J64" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="n">
-        <v>63.38</v>
+        <v>58</v>
       </c>
       <c r="Q64" t="n">
-        <v>72.78319999999999</v>
+        <v>62.2</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>62.4</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>47.1</v>
       </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
@@ -3390,89 +3586,109 @@
       <c r="W64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>clinc</t>
-        </is>
-      </c>
+      <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C65" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>78</v>
+        <v>46.75</v>
       </c>
       <c r="E65" t="n">
-        <v>68.4712</v>
+        <v>50.2914</v>
       </c>
       <c r="F65" t="n">
-        <v>68.0471</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>84.58499999999999</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>87.06999999999999</v>
+        <v>39.38</v>
       </c>
       <c r="I65" t="n">
-        <v>80.7998</v>
+        <v>56.1519</v>
       </c>
       <c r="J65" t="n">
-        <v>80.5347</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>90.87439999999999</v>
+        <v>0</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>63.38</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>72.78319999999999</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n"/>
-      <c r="B66" s="1" t="n"/>
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>clinc</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
       <c r="C66" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>77.2</v>
+        <v>78</v>
       </c>
       <c r="E66" t="n">
-        <v>66.76139999999999</v>
+        <v>68.4712</v>
       </c>
       <c r="F66" t="n">
-        <v>66.3121</v>
+        <v>68.0471</v>
       </c>
       <c r="G66" t="n">
-        <v>83.8347</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+        <v>84.58499999999999</v>
+      </c>
+      <c r="H66" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="I66" t="n">
+        <v>74.7923</v>
+      </c>
+      <c r="J66" t="n">
+        <v>74.8426</v>
+      </c>
+      <c r="K66" t="n">
+        <v>71.0213</v>
+      </c>
       <c r="L66" t="n">
-        <v>70.48999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="M66" t="n">
-        <v>70.7239</v>
+        <v>80.7998</v>
       </c>
       <c r="N66" t="n">
-        <v>70.71510000000001</v>
+        <v>80.5347</v>
       </c>
       <c r="O66" t="n">
-        <v>71.3852</v>
+        <v>90.87439999999999</v>
       </c>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
@@ -3485,54 +3701,42 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n"/>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
+      <c r="B67" s="1" t="n"/>
       <c r="C67" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>0.7466666666666667</v>
+        <v>77.2</v>
       </c>
       <c r="E67" t="n">
-        <v>0.0219220982579761</v>
+        <v>66.76139999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>66.3121</v>
       </c>
       <c r="G67" t="n">
-        <v>0.8549618320610687</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="n">
-        <v>0.6635555555555556</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0.4972864818903884</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0.4940369729759688</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0.740999650471863</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0.2533333333333333</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0.003577480700433</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0.4042553191489361</v>
-      </c>
+        <v>83.8347</v>
+      </c>
+      <c r="H67" t="n">
+        <v>70.48999999999999</v>
+      </c>
+      <c r="I67" t="n">
+        <v>70.7239</v>
+      </c>
+      <c r="J67" t="n">
+        <v>70.71510000000001</v>
+      </c>
+      <c r="K67" t="n">
+        <v>71.3852</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
@@ -3542,51 +3746,51 @@
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C68" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2453333333333333</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4532367071418627</v>
+        <v>0.0219220982579761</v>
       </c>
       <c r="F68" t="n">
-        <v>0.4633778493517164</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0678733031674208</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="n">
-        <v>0.4693333333333333</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0.594195117360772</v>
-      </c>
-      <c r="N68" t="n">
-        <v>0.5980151548230181</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0.3076923076923077</v>
-      </c>
+        <v>0.8549618320610687</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.6635555555555556</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.4972864818903884</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.4940369729759688</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.740999650471863</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
-        <v>0.5831111111111111</v>
+        <v>0.2533333333333333</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.6329349785950765</v>
+        <v>0.003577480700433</v>
       </c>
       <c r="R68" t="n">
-        <v>0.635149392377884</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.3849206349206349</v>
+        <v>0.4042553191489361</v>
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -3597,44 +3801,52 @@
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C69" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0.8368888888888889</v>
+        <v>0.2453333333333333</v>
       </c>
       <c r="E69" t="n">
-        <v>0.7864961634000692</v>
+        <v>0.4532367071418627</v>
       </c>
       <c r="F69" t="n">
-        <v>0.7840369134604483</v>
+        <v>0.4633778493517164</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8799476611056591</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="n">
-        <v>0.8244444444444444</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0.8673572235349517</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0.8682117156927298</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0.803270311701584</v>
-      </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
+        <v>0.0678733031674208</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.4693333333333333</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.594195117360772</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.5980151548230181</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>0.5831111111111111</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.6329349785950765</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.635149392377884</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0.3849206349206349</v>
+      </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
@@ -3642,38 +3854,42 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n"/>
-      <c r="B70" s="1" t="n"/>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
       <c r="C70" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>0.8484444444444444</v>
+        <v>0.8368888888888889</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8055937630884049</v>
+        <v>0.7864961634000692</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8033846868152448</v>
+        <v>0.7840369134604483</v>
       </c>
       <c r="G70" t="n">
-        <v>0.889538661468486</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0.8664748504619255</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0.8671765355395011</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0.8138484696437531</v>
-      </c>
+        <v>0.8799476611056591</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.8244444444444444</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.8673572235349517</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.8682117156927298</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.803270311701584</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -3685,30 +3901,34 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n"/>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>KnnCon</t>
-        </is>
-      </c>
+      <c r="B71" s="1" t="n"/>
       <c r="C71" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>86.76000000000001</v>
+        <v>0.8484444444444444</v>
       </c>
       <c r="E71" t="n">
-        <v>82.23999999999999</v>
+        <v>0.8055937630884049</v>
       </c>
       <c r="F71" t="n">
-        <v>82.03</v>
+        <v>0.8033846868152448</v>
       </c>
       <c r="G71" t="n">
-        <v>90.45999999999999</v>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+        <v>0.889538661468486</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.8664748504619255</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.8671765355395011</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.8138484696437531</v>
+      </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
@@ -3724,26 +3944,38 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n"/>
-      <c r="B72" s="1" t="n"/>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
       <c r="C72" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>88.04000000000001</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>84.48</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>84.3</v>
+        <v>82.03</v>
       </c>
       <c r="G72" t="n">
-        <v>91.41</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+        <v>90.45999999999999</v>
+      </c>
+      <c r="H72" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="I72" t="n">
+        <v>88.94</v>
+      </c>
+      <c r="J72" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="K72" t="n">
+        <v>85.34999999999999</v>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
@@ -3759,54 +3991,42 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n"/>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>ab</t>
-        </is>
-      </c>
+      <c r="B73" s="1" t="n"/>
       <c r="C73" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>82.59999999999999</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>67.7</v>
+        <v>84.48</v>
       </c>
       <c r="F73" t="n">
-        <v>67.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="G73" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="M73" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="N73" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="O73" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="P73" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="R73" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="S73" t="n">
-        <v>59</v>
-      </c>
+        <v>91.41</v>
+      </c>
+      <c r="H73" t="n">
+        <v>87.16</v>
+      </c>
+      <c r="I73" t="n">
+        <v>89.34999999999999</v>
+      </c>
+      <c r="J73" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="K73" t="n">
+        <v>86.05</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
@@ -3814,42 +4034,54 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n"/>
-      <c r="B74" s="1" t="n"/>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
       <c r="C74" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>82.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>66.3</v>
+        <v>67.7</v>
       </c>
       <c r="F74" t="n">
-        <v>65.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="H74" t="n">
         <v>73.3</v>
       </c>
-      <c r="M74" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="N74" t="n">
-        <v>69</v>
-      </c>
-      <c r="O74" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
+      <c r="I74" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="J74" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="K74" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="R74" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="S74" t="n">
+        <v>59</v>
+      </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
@@ -3857,136 +4089,152 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n"/>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B75" s="1" t="n"/>
       <c r="C75" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>36.44</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="E75" t="n">
-        <v>49.4399</v>
+        <v>66.3</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>65.8</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="n">
-        <v>53.51</v>
-      </c>
-      <c r="M75" t="n">
-        <v>71.02160000000001</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>74.89</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>85.5643</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
+        <v>88.8</v>
+      </c>
+      <c r="H75" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="I75" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="J75" t="n">
+        <v>69</v>
+      </c>
+      <c r="K75" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>hwu</t>
-        </is>
-      </c>
+      <c r="A76" s="1" t="n"/>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C76" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>67.73</v>
+        <v>36.44</v>
       </c>
       <c r="E76" t="n">
-        <v>47.2084</v>
+        <v>49.4399</v>
       </c>
       <c r="F76" t="n">
-        <v>45.2056</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>79.2534</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>81.40000000000001</v>
+        <v>53.51</v>
       </c>
       <c r="I76" t="n">
-        <v>73.509</v>
+        <v>71.02160000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>72.67610000000001</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>86.8347</v>
+        <v>0</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>74.89</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>85.5643</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n"/>
-      <c r="B77" s="1" t="n"/>
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>hwu</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
       <c r="C77" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>66.18000000000001</v>
+        <v>67.73</v>
       </c>
       <c r="E77" t="n">
-        <v>51.7591</v>
+        <v>47.2084</v>
       </c>
       <c r="F77" t="n">
-        <v>50.1787</v>
+        <v>45.2056</v>
       </c>
       <c r="G77" t="n">
-        <v>77.0468</v>
-      </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
+        <v>79.2534</v>
+      </c>
+      <c r="H77" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="I77" t="n">
+        <v>58.4396</v>
+      </c>
+      <c r="J77" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="K77" t="n">
+        <v>63.2258</v>
+      </c>
+      <c r="L77" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="M77" t="n">
+        <v>73.509</v>
+      </c>
+      <c r="N77" t="n">
+        <v>72.67610000000001</v>
+      </c>
+      <c r="O77" t="n">
+        <v>86.8347</v>
+      </c>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
@@ -3998,54 +4246,42 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n"/>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
+      <c r="B78" s="1" t="n"/>
       <c r="C78" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>0.7529069767441861</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0505316554482489</v>
+        <v>51.7591</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>50.1787</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8590381426202321</v>
-      </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="n">
-        <v>0.5281007751937985</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0.0209450241156011</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0.6911857958148383</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0.2761627906976744</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0.008832690251499201</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0.4328018223234624</v>
-      </c>
+        <v>77.0468</v>
+      </c>
+      <c r="H78" t="n">
+        <v>66.18000000000001</v>
+      </c>
+      <c r="I78" t="n">
+        <v>65.9492</v>
+      </c>
+      <c r="J78" t="n">
+        <v>65.8686</v>
+      </c>
+      <c r="K78" t="n">
+        <v>68.52849999999999</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
@@ -4055,51 +4291,51 @@
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C79" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1744186046511628</v>
+        <v>0.7529069767441861</v>
       </c>
       <c r="E79" t="n">
-        <v>0.4553564822398199</v>
+        <v>0.0505316554482489</v>
       </c>
       <c r="F79" t="n">
-        <v>0.4838162623798087</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="n">
-        <v>0.4467054263565891</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0.5746710012582736</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0.5815240981467681</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0.3553719008264462</v>
-      </c>
+        <v>0.8590381426202321</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.5281007751937985</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.0209450241156011</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.6911857958148383</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
       <c r="P79" t="n">
-        <v>0.4835271317829457</v>
+        <v>0.2761627906976744</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.5904012685899459</v>
+        <v>0.008832690251499201</v>
       </c>
       <c r="R79" t="n">
-        <v>0.6011118308953792</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0762942779291553</v>
+        <v>0.4328018223234624</v>
       </c>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
@@ -4110,36 +4346,52 @@
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C80" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0.7015503875968992</v>
+        <v>0.1744186046511628</v>
       </c>
       <c r="E80" t="n">
-        <v>0.6738222157721238</v>
+        <v>0.4553564822398199</v>
       </c>
       <c r="F80" t="n">
-        <v>0.6680616892812824</v>
+        <v>0.4838162623798087</v>
       </c>
       <c r="G80" t="n">
-        <v>0.765990639625585</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.4467054263565891</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.5746710012582736</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.5815240981467681</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.3553719008264462</v>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
+      <c r="P80" t="n">
+        <v>0.4835271317829457</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0.5904012685899459</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.6011118308953792</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0.0762942779291553</v>
+      </c>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
@@ -4147,26 +4399,38 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n"/>
-      <c r="B81" s="1" t="n"/>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
       <c r="C81" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0.6908914728682171</v>
+        <v>0.7015503875968992</v>
       </c>
       <c r="E81" t="n">
-        <v>0.6506487139546074</v>
+        <v>0.6738222157721238</v>
       </c>
       <c r="F81" t="n">
-        <v>0.6439208936478604</v>
+        <v>0.6680616892812824</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7582938388625592</v>
-      </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+        <v>0.765990639625585</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.687984496124031</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.8353868443901223</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.8418348201320556</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.6290516206482593</v>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
@@ -4182,30 +4446,34 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n"/>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>KnnCon</t>
-        </is>
-      </c>
+      <c r="B82" s="1" t="n"/>
       <c r="C82" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>81.40000000000001</v>
+        <v>0.6908914728682171</v>
       </c>
       <c r="E82" t="n">
-        <v>74.45</v>
+        <v>0.6506487139546074</v>
       </c>
       <c r="F82" t="n">
-        <v>73.68000000000001</v>
+        <v>0.6439208936478604</v>
       </c>
       <c r="G82" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+        <v>0.7582938388625592</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.748062015503876</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.7840318684280044</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.786023860714939</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.7202881152460985</v>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
@@ -4221,26 +4489,38 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n"/>
-      <c r="B83" s="1" t="n"/>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
       <c r="C83" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>82.56</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E83" t="n">
-        <v>75.22</v>
+        <v>74.45</v>
       </c>
       <c r="F83" t="n">
-        <v>74.45</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>87.52</v>
-      </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+        <v>86.7</v>
+      </c>
+      <c r="H83" t="n">
+        <v>76.26000000000001</v>
+      </c>
+      <c r="I83" t="n">
+        <v>86.17</v>
+      </c>
+      <c r="J83" t="n">
+        <v>86.53</v>
+      </c>
+      <c r="K83" t="n">
+        <v>74.78</v>
+      </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
@@ -4256,37 +4536,33 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n"/>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>SCL</t>
-        </is>
-      </c>
+      <c r="B84" s="1" t="n"/>
       <c r="C84" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>0.7529069767441861</v>
+        <v>82.56</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0505316554482489</v>
+        <v>75.22</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>74.45</v>
       </c>
       <c r="G84" t="n">
-        <v>0.8590381426202321</v>
+        <v>87.52</v>
       </c>
       <c r="H84" t="n">
-        <v>0.7529069767441861</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0505316554482489</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>0.8590381426202321</v>
+        <v>79.5</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
@@ -4303,30 +4579,50 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n"/>
-      <c r="B85" s="1" t="n"/>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
       <c r="C85" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0.7267441860465116</v>
+        <v>0.7529069767441861</v>
       </c>
       <c r="E85" t="n">
-        <v>0.0495147553971083</v>
+        <v>0.0505316554482489</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.8417508417508418</v>
-      </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
+        <v>0.8590381426202321</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.5281007751937985</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.0209450241156011</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.6911857958148383</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.7529069767441861</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.0505316554482489</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.8590381426202321</v>
+      </c>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -4338,54 +4634,34 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n"/>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>ab</t>
-        </is>
-      </c>
+      <c r="B86" s="1" t="n"/>
       <c r="C86" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>85.90000000000001</v>
+        <v>0.7267441860465116</v>
       </c>
       <c r="E86" t="n">
-        <v>62.5</v>
+        <v>0.0495147553971083</v>
       </c>
       <c r="F86" t="n">
-        <v>60.7</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>92.40000000000001</v>
+        <v>0.8417508417508418</v>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="n">
-        <v>78</v>
-      </c>
-      <c r="M86" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="N86" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="O86" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="P86" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="R86" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="S86" t="n">
-        <v>65.59999999999999</v>
-      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
@@ -4393,34 +4669,54 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n"/>
-      <c r="B87" s="1" t="n"/>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
       <c r="C87" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>80.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="E87" t="n">
-        <v>57</v>
+        <v>62.5</v>
       </c>
       <c r="F87" t="n">
-        <v>55.1</v>
+        <v>60.7</v>
       </c>
       <c r="G87" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+        <v>92.40000000000001</v>
+      </c>
+      <c r="H87" t="n">
+        <v>78</v>
+      </c>
+      <c r="I87" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="J87" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="K87" t="n">
+        <v>84.09999999999999</v>
+      </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
+      <c r="P87" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="R87" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="S87" t="n">
+        <v>65.59999999999999</v>
+      </c>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
@@ -4428,30 +4724,34 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n"/>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B88" s="1" t="n"/>
       <c r="C88" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>20.45</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E88" t="n">
-        <v>36.1465</v>
+        <v>57</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>55.1</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+        <v>88.90000000000001</v>
+      </c>
+      <c r="H88" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="I88" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="J88" t="n">
+        <v>59</v>
+      </c>
+      <c r="K88" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
@@ -4466,35 +4766,31 @@
       <c r="W88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="inlineStr">
-        <is>
-          <t>mcid</t>
-        </is>
-      </c>
+      <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C89" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="n">
-        <v>67.37</v>
-      </c>
-      <c r="I89" t="n">
-        <v>69.4192</v>
-      </c>
-      <c r="J89" t="n">
-        <v>68.3593</v>
-      </c>
-      <c r="K89" t="n">
-        <v>73.6585</v>
-      </c>
+      <c r="D89" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="E89" t="n">
+        <v>36.1465</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
@@ -4509,55 +4805,43 @@
       <c r="W89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n"/>
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>ADB</t>
         </is>
       </c>
       <c r="C90" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D90" t="n">
-        <v>0.7552870090634441</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0.1721170395869191</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>0.8605851979345955</v>
-      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="n">
-        <v>0.5075528700906344</v>
+        <v>67.37</v>
       </c>
       <c r="M90" t="n">
-        <v>0.07481629926519701</v>
+        <v>69.4192</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>68.3593</v>
       </c>
       <c r="O90" t="n">
-        <v>0.6733466933867736</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0.256797583081571</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0.0314349112426035</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0.4086538461538461</v>
-      </c>
+        <v>73.6585</v>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
@@ -4567,51 +4851,51 @@
       <c r="A91" s="1" t="n"/>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C91" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0.2779456193353474</v>
+        <v>0.7552870090634441</v>
       </c>
       <c r="E91" t="n">
-        <v>0.3419706628197066</v>
+        <v>0.1721170395869191</v>
       </c>
       <c r="F91" t="n">
-        <v>0.3664072229140722</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.2442244224422442</v>
-      </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="n">
-        <v>0.3897280966767371</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0.4761358567823756</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0.5114982495081919</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0.1932367149758454</v>
-      </c>
+        <v>0.8605851979345955</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.5075528700906344</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.07481629926519701</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.6733466933867736</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
-        <v>0.5226586102719033</v>
+        <v>0.256797583081571</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.5884257251366416</v>
+        <v>0.0314349112426035</v>
       </c>
       <c r="R91" t="n">
-        <v>0.6374612022313617</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>0.4086538461538461</v>
       </c>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
@@ -4622,36 +4906,52 @@
       <c r="A92" s="1" t="n"/>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C92" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.7341389728096677</v>
+        <v>0.2779456193353474</v>
       </c>
       <c r="E92" t="n">
-        <v>0.7266145439925927</v>
+        <v>0.3419706628197066</v>
       </c>
       <c r="F92" t="n">
-        <v>0.7111527953753564</v>
+        <v>0.3664072229140722</v>
       </c>
       <c r="G92" t="n">
-        <v>0.7884615384615384</v>
-      </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+        <v>0.2442244224422442</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.3897280966767371</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.4761358567823756</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.5114982495081919</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.1932367149758454</v>
+      </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
+      <c r="P92" t="n">
+        <v>0.5226586102719033</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0.5884257251366416</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0.6374612022313617</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
@@ -4659,26 +4959,38 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n"/>
-      <c r="B93" s="1" t="n"/>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
       <c r="C93" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0.6012084592145015</v>
+        <v>0.7341389728096677</v>
       </c>
       <c r="E93" t="n">
-        <v>0.5569695272048214</v>
+        <v>0.7266145439925927</v>
       </c>
       <c r="F93" t="n">
-        <v>0.5304365079365079</v>
+        <v>0.7111527953753564</v>
       </c>
       <c r="G93" t="n">
-        <v>0.6631016042780749</v>
-      </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+        <v>0.7884615384615384</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.7311178247734139</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.7952810500249099</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.8089247579203594</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.6861313868613139</v>
+      </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
@@ -4694,30 +5006,34 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n"/>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>KnnCon</t>
-        </is>
-      </c>
+      <c r="B94" s="1" t="n"/>
       <c r="C94" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>66.47</v>
+        <v>0.6012084592145015</v>
       </c>
       <c r="E94" t="n">
-        <v>70.43000000000001</v>
+        <v>0.5569695272048214</v>
       </c>
       <c r="F94" t="n">
-        <v>70.09</v>
+        <v>0.5304365079365079</v>
       </c>
       <c r="G94" t="n">
-        <v>71.76000000000001</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+        <v>0.6631016042780749</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.7522658610271903</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.7695944535708862</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.772936617410104</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.7428571428571429</v>
+      </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
@@ -4733,26 +5049,38 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n"/>
-      <c r="B95" s="1" t="n"/>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
       <c r="C95" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>78.25</v>
+        <v>66.47</v>
       </c>
       <c r="E95" t="n">
-        <v>71.45999999999999</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="F95" t="n">
-        <v>68.2</v>
+        <v>70.09</v>
       </c>
       <c r="G95" t="n">
-        <v>84.51000000000001</v>
-      </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+        <v>71.76000000000001</v>
+      </c>
+      <c r="H95" t="n">
+        <v>81.27</v>
+      </c>
+      <c r="I95" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="J95" t="n">
+        <v>83.62</v>
+      </c>
+      <c r="K95" t="n">
+        <v>81.25</v>
+      </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
@@ -4768,54 +5096,42 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n"/>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>ab</t>
-        </is>
-      </c>
+      <c r="B96" s="1" t="n"/>
       <c r="C96" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
-        <v>72.5</v>
+        <v>78.25</v>
       </c>
       <c r="E96" t="n">
-        <v>49.5</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>41.3</v>
+        <v>68.2</v>
       </c>
       <c r="G96" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="M96" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="N96" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="O96" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="P96" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="R96" t="n">
-        <v>43</v>
-      </c>
-      <c r="S96" t="n">
-        <v>41.8</v>
-      </c>
+        <v>84.51000000000001</v>
+      </c>
+      <c r="H96" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="I96" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>80.34</v>
+      </c>
+      <c r="K96" t="n">
+        <v>80</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
@@ -4823,34 +5139,54 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n"/>
-      <c r="B97" s="1" t="n"/>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
       <c r="C97" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>74.3</v>
+        <v>72.5</v>
       </c>
       <c r="E97" t="n">
-        <v>46.8</v>
+        <v>49.5</v>
       </c>
       <c r="F97" t="n">
-        <v>37.3</v>
+        <v>41.3</v>
       </c>
       <c r="G97" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+        <v>82.3</v>
+      </c>
+      <c r="H97" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="I97" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="J97" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="K97" t="n">
+        <v>67.59999999999999</v>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
+      <c r="P97" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="R97" t="n">
+        <v>43</v>
+      </c>
+      <c r="S97" t="n">
+        <v>41.8</v>
+      </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
@@ -4858,128 +5194,144 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n"/>
-      <c r="B98" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B98" s="1" t="n"/>
       <c r="C98" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="n">
-        <v>51.36</v>
-      </c>
-      <c r="M98" t="n">
-        <v>60.1486</v>
-      </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="n">
-        <v>59.82</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>67.8672</v>
-      </c>
-      <c r="R98" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D98" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="E98" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="F98" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="G98" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="H98" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="I98" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="J98" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="K98" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="A99" s="1" t="n"/>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C99" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D99" t="n">
-        <v>47.28</v>
-      </c>
-      <c r="E99" t="n">
-        <v>49.4819</v>
-      </c>
-      <c r="F99" t="n">
-        <v>49.0176</v>
-      </c>
-      <c r="G99" t="n">
-        <v>51.8033</v>
-      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>72</v>
+        <v>51.36</v>
       </c>
       <c r="I99" t="n">
-        <v>66.20140000000001</v>
+        <v>60.1486</v>
       </c>
       <c r="J99" t="n">
-        <v>63.7654</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>78.3813</v>
+        <v>0</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
+      <c r="P99" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>67.8672</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n"/>
-      <c r="B100" s="1" t="n"/>
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
       <c r="C100" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>35.49</v>
+        <v>47.28</v>
       </c>
       <c r="E100" t="n">
-        <v>43.0567</v>
+        <v>49.4819</v>
       </c>
       <c r="F100" t="n">
-        <v>45.2942</v>
+        <v>49.0176</v>
       </c>
       <c r="G100" t="n">
-        <v>31.869</v>
-      </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
+        <v>51.8033</v>
+      </c>
+      <c r="H100" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="I100" t="n">
+        <v>60.2584</v>
+      </c>
+      <c r="J100" t="n">
+        <v>61.8529</v>
+      </c>
+      <c r="K100" t="n">
+        <v>44.3137</v>
+      </c>
+      <c r="L100" t="n">
+        <v>72</v>
+      </c>
+      <c r="M100" t="n">
+        <v>66.20140000000001</v>
+      </c>
+      <c r="N100" t="n">
+        <v>63.7654</v>
+      </c>
+      <c r="O100" t="n">
+        <v>78.3813</v>
+      </c>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
@@ -4991,54 +5343,42 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n"/>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
+      <c r="B101" s="1" t="n"/>
       <c r="C101" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>0.738</v>
+        <v>35.49</v>
       </c>
       <c r="E101" t="n">
-        <v>0.1415420023014959</v>
+        <v>43.0567</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>45.2942</v>
       </c>
       <c r="G101" t="n">
-        <v>0.8492520138089759</v>
-      </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="n">
-        <v>0.5335</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0.1907518468249577</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0.1420480951153784</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0.6777893639207507</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0.0233739837398373</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="n">
-        <v>0.3739837398373983</v>
-      </c>
+        <v>31.869</v>
+      </c>
+      <c r="H101" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="I101" t="n">
+        <v>56.7415</v>
+      </c>
+      <c r="J101" t="n">
+        <v>59.6117</v>
+      </c>
+      <c r="K101" t="n">
+        <v>28.0394</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
@@ -5048,51 +5388,51 @@
       <c r="A102" s="1" t="n"/>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C102" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0.754</v>
+        <v>0.738</v>
       </c>
       <c r="E102" t="n">
-        <v>0.2397471839495868</v>
+        <v>0.1415420023014959</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1163012719022949</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>0.8569767441860465</v>
-      </c>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="n">
-        <v>0.5245</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0.2092355085673985</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0.1633289368321943</v>
-      </c>
-      <c r="O102" t="n">
-        <v>0.6683012259194396</v>
-      </c>
+        <v>0.8492520138089759</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.5335</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.1907518468249577</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.1420480951153784</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.6777893639207507</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
       <c r="P102" t="n">
-        <v>0.3655</v>
+        <v>0.23</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.3057995984319704</v>
+        <v>0.0233739837398373</v>
       </c>
       <c r="R102" t="n">
-        <v>0.2997691816451678</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>0.3962558502340094</v>
+        <v>0.3739837398373983</v>
       </c>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
@@ -5103,36 +5443,52 @@
       <c r="A103" s="1" t="n"/>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C103" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>0.543</v>
+        <v>0.754</v>
       </c>
       <c r="E103" t="n">
-        <v>0.5499067233508657</v>
+        <v>0.2397471839495868</v>
       </c>
       <c r="F103" t="n">
-        <v>0.5462604288655685</v>
+        <v>0.1163012719022949</v>
       </c>
       <c r="G103" t="n">
-        <v>0.5681381957773513</v>
-      </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
+        <v>0.8569767441860465</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.5245</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.2092355085673985</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.1633289368321943</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.6683012259194396</v>
+      </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
+      <c r="P103" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0.3057995984319704</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.2997691816451678</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0.3962558502340094</v>
+      </c>
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
@@ -5140,26 +5496,38 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n"/>
-      <c r="B104" s="1" t="n"/>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
       <c r="C104" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>0.5255</v>
+        <v>0.543</v>
       </c>
       <c r="E104" t="n">
-        <v>0.5344507295147621</v>
+        <v>0.5499067233508657</v>
       </c>
       <c r="F104" t="n">
-        <v>0.5334229868546647</v>
+        <v>0.5462604288655685</v>
       </c>
       <c r="G104" t="n">
-        <v>0.5395894428152492</v>
-      </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+        <v>0.5681381957773513</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.6906405634268898</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.7152601753251344</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.4444444444444444</v>
+      </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
@@ -5175,30 +5543,34 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n"/>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>KnnCon</t>
-        </is>
-      </c>
+      <c r="B105" s="1" t="n"/>
       <c r="C105" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>69.84999999999999</v>
+        <v>0.5255</v>
       </c>
       <c r="E105" t="n">
-        <v>67.54000000000001</v>
+        <v>0.5344507295147621</v>
       </c>
       <c r="F105" t="n">
-        <v>65.97</v>
+        <v>0.5334229868546647</v>
       </c>
       <c r="G105" t="n">
-        <v>75.38</v>
-      </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
+        <v>0.5395894428152492</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.6258832268106558</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.6660606836173582</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.2241086587436332</v>
+      </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
@@ -5214,21 +5586,25 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n"/>
-      <c r="B106" s="1" t="n"/>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
       <c r="C106" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>74.90000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="E106" t="n">
-        <v>72.16</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="F106" t="n">
-        <v>70.58</v>
+        <v>65.97</v>
       </c>
       <c r="G106" t="n">
-        <v>80.05</v>
+        <v>75.38</v>
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
@@ -5249,37 +5625,33 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n"/>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>SCL</t>
-        </is>
-      </c>
+      <c r="B107" s="1" t="n"/>
       <c r="C107" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
-        <v>0.738</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E107" t="n">
-        <v>0.1415420023014959</v>
+        <v>72.16</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>70.58</v>
       </c>
       <c r="G107" t="n">
-        <v>0.8492520138089759</v>
+        <v>80.05</v>
       </c>
       <c r="H107" t="n">
-        <v>0.738</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1415420023014959</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>73.23</v>
       </c>
       <c r="K107" t="n">
-        <v>0.8492520138089759</v>
+        <v>58.05</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
@@ -5296,30 +5668,50 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n"/>
-      <c r="B108" s="1" t="n"/>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
       <c r="C108" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>0.7385</v>
+        <v>0.738</v>
       </c>
       <c r="E108" t="n">
-        <v>0.1415971623046687</v>
+        <v>0.1415420023014959</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8495829738280126</v>
-      </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
+        <v>0.8492520138089759</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.0599561296612234</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.6595174262734584</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.1415420023014959</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.8492520138089759</v>
+      </c>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
@@ -5331,54 +5723,42 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n"/>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>ab</t>
-        </is>
-      </c>
+      <c r="B109" s="1" t="n"/>
       <c r="C109" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D109" t="n">
-        <v>66.7</v>
+        <v>0.7385</v>
       </c>
       <c r="E109" t="n">
-        <v>49.3</v>
+        <v>0.1415971623046687</v>
       </c>
       <c r="F109" t="n">
-        <v>43.7</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="M109" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="N109" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="O109" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="P109" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="R109" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="S109" t="n">
-        <v>40</v>
-      </c>
+        <v>0.8495829738280126</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.0611690897025999</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.6728599867285998</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
@@ -5386,34 +5766,54 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n"/>
-      <c r="B110" s="1" t="n"/>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
       <c r="C110" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>67.3</v>
+        <v>66.7</v>
       </c>
       <c r="E110" t="n">
-        <v>49.9</v>
+        <v>49.3</v>
       </c>
       <c r="F110" t="n">
-        <v>44.3</v>
+        <v>43.7</v>
       </c>
       <c r="G110" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+        <v>77.7</v>
+      </c>
+      <c r="H110" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="I110" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J110" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K110" t="n">
+        <v>58.5</v>
+      </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
+      <c r="P110" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="R110" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="S110" t="n">
+        <v>40</v>
+      </c>
       <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
@@ -5421,136 +5821,152 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n"/>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B111" s="1" t="n"/>
       <c r="C111" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D111" t="n">
-        <v>30.8</v>
+        <v>67.3</v>
       </c>
       <c r="E111" t="n">
-        <v>38.4882</v>
+        <v>49.9</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>44.3</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="n">
-        <v>49.65</v>
-      </c>
-      <c r="M111" t="n">
-        <v>59.761</v>
-      </c>
-      <c r="N111" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="n">
-        <v>62.45</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>67.5523</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" t="n">
-        <v>0</v>
-      </c>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="H111" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="I111" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="J111" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="K111" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="inlineStr">
-        <is>
-          <t>stackoverflow</t>
-        </is>
-      </c>
+      <c r="A112" s="1" t="n"/>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C112" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>66.15000000000001</v>
+        <v>30.8</v>
       </c>
       <c r="E112" t="n">
-        <v>63.7554</v>
+        <v>38.4882</v>
       </c>
       <c r="F112" t="n">
-        <v>61.5881</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>74.59229999999999</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>80.79000000000001</v>
+        <v>49.65</v>
       </c>
       <c r="I112" t="n">
-        <v>73.0835</v>
+        <v>59.761</v>
       </c>
       <c r="J112" t="n">
-        <v>70.32259999999999</v>
+        <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>86.88800000000001</v>
+        <v>0</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
+      <c r="P112" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>67.5523</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n"/>
-      <c r="B113" s="1" t="n"/>
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>ADB</t>
+        </is>
+      </c>
       <c r="C113" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>77.67</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="E113" t="n">
-        <v>72.7028</v>
+        <v>63.7554</v>
       </c>
       <c r="F113" t="n">
-        <v>70.43940000000001</v>
+        <v>61.5881</v>
       </c>
       <c r="G113" t="n">
-        <v>84.01990000000001</v>
-      </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
+        <v>74.59229999999999</v>
+      </c>
+      <c r="H113" t="n">
+        <v>81.17</v>
+      </c>
+      <c r="I113" t="n">
+        <v>80.11</v>
+      </c>
+      <c r="J113" t="n">
+        <v>79.79940000000001</v>
+      </c>
+      <c r="K113" t="n">
+        <v>83.2166</v>
+      </c>
+      <c r="L113" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="M113" t="n">
+        <v>73.0835</v>
+      </c>
+      <c r="N113" t="n">
+        <v>70.32259999999999</v>
+      </c>
+      <c r="O113" t="n">
+        <v>86.88800000000001</v>
+      </c>
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
@@ -5562,54 +5978,42 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n"/>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
+      <c r="B114" s="1" t="n"/>
       <c r="C114" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D114" t="n">
-        <v>0.7552996160908029</v>
+        <v>77.67</v>
       </c>
       <c r="E114" t="n">
-        <v>0.6125494108169093</v>
+        <v>72.7028</v>
       </c>
       <c r="F114" t="n">
-        <v>0.5663624416817391</v>
+        <v>70.43940000000001</v>
       </c>
       <c r="G114" t="n">
-        <v>0.8434842564927603</v>
-      </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="n">
-        <v>0.7347688198965114</v>
-      </c>
-      <c r="M114" t="n">
-        <v>0.6875742279523628</v>
-      </c>
-      <c r="N114" t="n">
-        <v>0.6783958153965095</v>
-      </c>
-      <c r="O114" t="n">
-        <v>0.7793583535108959</v>
-      </c>
-      <c r="P114" t="n">
-        <v>0.6890335503254882</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>0.7203835290749597</v>
-      </c>
-      <c r="R114" t="n">
-        <v>0.727683731719721</v>
-      </c>
-      <c r="S114" t="n">
-        <v>0.6108804894035395</v>
-      </c>
+        <v>84.01990000000001</v>
+      </c>
+      <c r="H114" t="n">
+        <v>85.76000000000001</v>
+      </c>
+      <c r="I114" t="n">
+        <v>84.2179</v>
+      </c>
+      <c r="J114" t="n">
+        <v>83.9166</v>
+      </c>
+      <c r="K114" t="n">
+        <v>87.23050000000001</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
@@ -5619,51 +6023,51 @@
       <c r="A115" s="1" t="n"/>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>DeepUnk</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="C115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>0.7606409614421632</v>
+        <v>0.7552996160908029</v>
       </c>
       <c r="E115" t="n">
-        <v>0.3466582912392981</v>
+        <v>0.6125494108169093</v>
       </c>
       <c r="F115" t="n">
-        <v>0.2444188771679557</v>
+        <v>0.5663624416817391</v>
       </c>
       <c r="G115" t="n">
-        <v>0.8578553615960099</v>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="n">
-        <v>0.5751961275246202</v>
-      </c>
-      <c r="M115" t="n">
-        <v>0.3025259371014686</v>
-      </c>
-      <c r="N115" t="n">
-        <v>0.2626832030488756</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0.7009532776273979</v>
-      </c>
+        <v>0.8434842564927603</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.7347688198965114</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.6875742279523628</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.6783958153965095</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.7793583535108959</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
       <c r="P115" t="n">
-        <v>0.3994324820564179</v>
+        <v>0.6890335503254882</v>
       </c>
       <c r="Q115" t="n">
-        <v>0.3302283193178961</v>
+        <v>0.7203835290749597</v>
       </c>
       <c r="R115" t="n">
-        <v>0.3220567764969455</v>
+        <v>0.727683731719721</v>
       </c>
       <c r="S115" t="n">
-        <v>0.4528014616321559</v>
+        <v>0.6108804894035395</v>
       </c>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
@@ -5674,36 +6078,52 @@
       <c r="A116" s="1" t="n"/>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>DyEn</t>
+          <t>DeepUnk</t>
         </is>
       </c>
       <c r="C116" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>0.4453346686696712</v>
+        <v>0.7606409614421632</v>
       </c>
       <c r="E116" t="n">
-        <v>0.4807412920773473</v>
+        <v>0.3466582912392981</v>
       </c>
       <c r="F116" t="n">
-        <v>0.4862991131948756</v>
+        <v>0.2444188771679557</v>
       </c>
       <c r="G116" t="n">
-        <v>0.4529521864897056</v>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+        <v>0.8578553615960099</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.5751961275246202</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.3025259371014686</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.2626832030488756</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0.7009532776273979</v>
+      </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
+      <c r="P116" t="n">
+        <v>0.3994324820564179</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0.3302283193178961</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0.3220567764969455</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0.4528014616321559</v>
+      </c>
       <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
@@ -5711,26 +6131,38 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n"/>
-      <c r="B117" s="1" t="n"/>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>DyEn</t>
+        </is>
+      </c>
       <c r="C117" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>0.599899849774662</v>
+        <v>0.4453346686696712</v>
       </c>
       <c r="E117" t="n">
-        <v>0.6214129244594941</v>
+        <v>0.4807412920773473</v>
       </c>
       <c r="F117" t="n">
-        <v>0.6156925533951411</v>
+        <v>0.4862991131948756</v>
       </c>
       <c r="G117" t="n">
-        <v>0.6500147797812592</v>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+        <v>0.4529521864897056</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.6504757135703555</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.7230268845218966</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.7394737171182304</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.5585585585585585</v>
+      </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
@@ -5746,30 +6178,34 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n"/>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>KnnCon</t>
-        </is>
-      </c>
+      <c r="B118" s="1" t="n"/>
       <c r="C118" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>58.52</v>
+        <v>0.599899849774662</v>
       </c>
       <c r="E118" t="n">
-        <v>57.44</v>
+        <v>0.6214129244594941</v>
       </c>
       <c r="F118" t="n">
-        <v>55.96</v>
+        <v>0.6156925533951411</v>
       </c>
       <c r="G118" t="n">
-        <v>64.84999999999999</v>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+        <v>0.6500147797812592</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.6960440660991487</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.7427075204798436</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.754112392230755</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.6286588029707296</v>
+      </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
@@ -5785,26 +6221,38 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n"/>
-      <c r="B119" s="1" t="n"/>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t>KnnCon</t>
+        </is>
+      </c>
       <c r="C119" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>73.19</v>
+        <v>58.52</v>
       </c>
       <c r="E119" t="n">
-        <v>70.20999999999999</v>
+        <v>57.44</v>
       </c>
       <c r="F119" t="n">
-        <v>68.42</v>
+        <v>55.96</v>
       </c>
       <c r="G119" t="n">
-        <v>79.15000000000001</v>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
+        <v>64.84999999999999</v>
+      </c>
+      <c r="H119" t="n">
+        <v>78.03</v>
+      </c>
+      <c r="I119" t="n">
+        <v>80.45</v>
+      </c>
+      <c r="J119" t="n">
+        <v>80.73</v>
+      </c>
+      <c r="K119" t="n">
+        <v>77.64</v>
+      </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
@@ -5820,54 +6268,42 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n"/>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>ab</t>
-        </is>
-      </c>
+      <c r="B120" s="1" t="n"/>
       <c r="C120" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>73.7</v>
+        <v>73.19</v>
       </c>
       <c r="E120" t="n">
-        <v>58.1</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="F120" t="n">
-        <v>53.1</v>
+        <v>68.42</v>
       </c>
       <c r="G120" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="M120" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="N120" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="O120" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="P120" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="R120" t="n">
-        <v>66</v>
-      </c>
-      <c r="S120" t="n">
-        <v>53.5</v>
-      </c>
+        <v>79.15000000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>83.31</v>
+      </c>
+      <c r="I120" t="n">
+        <v>83.92</v>
+      </c>
+      <c r="J120" t="n">
+        <v>83.98</v>
+      </c>
+      <c r="K120" t="n">
+        <v>83.31999999999999</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
@@ -5875,42 +6311,54 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n"/>
-      <c r="B121" s="1" t="n"/>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
       <c r="C121" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>80</v>
+        <v>73.7</v>
       </c>
       <c r="E121" t="n">
-        <v>65.40000000000001</v>
+        <v>58.1</v>
       </c>
       <c r="F121" t="n">
-        <v>61</v>
+        <v>53.1</v>
       </c>
       <c r="G121" t="n">
-        <v>87</v>
-      </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="M121" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="N121" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="O121" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
+        <v>83.2</v>
+      </c>
+      <c r="H121" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="I121" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="J121" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="K121" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="R121" t="n">
+        <v>66</v>
+      </c>
+      <c r="S121" t="n">
+        <v>53.5</v>
+      </c>
       <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr"/>
@@ -5918,112 +6366,96 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n"/>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>clap</t>
-        </is>
-      </c>
+      <c r="B122" s="1" t="n"/>
       <c r="C122" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D122" t="n">
-        <v>31.11</v>
+        <v>80</v>
       </c>
       <c r="E122" t="n">
-        <v>47.2715</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="n">
-        <v>43.97</v>
-      </c>
-      <c r="M122" t="n">
-        <v>59.0736</v>
-      </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="n">
-        <v>80.77</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>84.18899999999999</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="n">
-        <v>0</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="H122" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="I122" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="J122" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="K122" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
       <c r="W122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="inlineStr">
-        <is>
-          <t>thucnews</t>
-        </is>
-      </c>
+      <c r="A123" s="1" t="n"/>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C123" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>32.7</v>
+        <v>31.11</v>
       </c>
       <c r="E123" t="n">
-        <v>26.7</v>
+        <v>47.2715</v>
       </c>
       <c r="F123" t="n">
-        <v>22.6</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="M123" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="N123" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="O123" t="n">
-        <v>43.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="I123" t="n">
+        <v>59.0736</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
       <c r="P123" t="n">
-        <v>27.1</v>
+        <v>80.77</v>
       </c>
       <c r="Q123" t="n">
-        <v>24.8</v>
+        <v>84.18899999999999</v>
       </c>
       <c r="R123" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
@@ -6031,125 +6463,185 @@
       <c r="W123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n"/>
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>clap</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C124" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>22.94</v>
+        <v>32.7</v>
       </c>
       <c r="E124" t="n">
-        <v>32.5598</v>
+        <v>26.7</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>22.6</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="n">
-        <v>35.19</v>
-      </c>
-      <c r="M124" t="n">
-        <v>43.5344</v>
-      </c>
-      <c r="N124" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0</v>
-      </c>
+        <v>43.1</v>
+      </c>
+      <c r="H124" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="I124" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="J124" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="K124" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
       <c r="P124" t="n">
-        <v>50.32</v>
+        <v>27.1</v>
       </c>
       <c r="Q124" t="n">
-        <v>54.4698</v>
+        <v>24.8</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
       <c r="W124" t="inlineStr"/>
     </row>
+    <row r="125">
+      <c r="A125" s="1" t="n"/>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>clap</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="E125" t="n">
+        <v>32.5598</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>35.19</v>
+      </c>
+      <c r="I125" t="n">
+        <v>43.5344</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>54.4698</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+      <c r="W125" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="64">
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="B43:B44"/>
+  <mergeCells count="65">
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="A66:A76"/>
+    <mergeCell ref="B72:B73"/>
     <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="D1:K1"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="B77:B78"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="A99:A111"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="A65:A75"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="A30:A39"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B117:B118"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="A113:A123"/>
     <mergeCell ref="L2:O2"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="B34:B35"/>
     <mergeCell ref="B28:B29"/>
-    <mergeCell ref="H1:K1"/>
-    <mergeCell ref="A76:A88"/>
-    <mergeCell ref="A112:A122"/>
+    <mergeCell ref="B119:B120"/>
     <mergeCell ref="B24:B25"/>
+    <mergeCell ref="P1:S1"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B44:B45"/>
     <mergeCell ref="A5:A17"/>
-    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="B53:B54"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="L1:S1"/>
-    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A100:A112"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="A53:A65"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="A90:A99"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="B59:B60"/>
     <mergeCell ref="D2:G2"/>
+    <mergeCell ref="B40:B41"/>
     <mergeCell ref="P2:S2"/>
-    <mergeCell ref="A89:A98"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="A30:A38"/>
-    <mergeCell ref="A52:A64"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="A40:A52"/>
+    <mergeCell ref="B113:B114"/>
     <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A39:A51"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="A77:A89"/>
     <mergeCell ref="H2:K2"/>
-    <mergeCell ref="B56:B57"/>
     <mergeCell ref="T2:W2"/>
-    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="B50:B51"/>
     <mergeCell ref="A18:A29"/>
     <mergeCell ref="B26:B27"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="L1:O1"/>
     <mergeCell ref="T1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/openset_pivot.xlsx
+++ b/results/openset_pivot.xlsx
@@ -2138,10 +2138,18 @@
       <c r="W16" t="n">
         <v>0.9096437880104256</v>
       </c>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
+      <c r="X16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.8937408390564399</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.8999289725841433</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.8009188361408882</v>
+      </c>
       <c r="AB16" t="n">
         <v>0.9675</v>
       </c>
@@ -2166,10 +2174,18 @@
       <c r="AI16" t="n">
         <v>0.9570383912248628</v>
       </c>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
+      <c r="AJ16" t="n">
+        <v>0.9685</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.976709440243004</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.9789439319309808</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.9431920649233544</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -2237,10 +2253,18 @@
       <c r="W17" t="n">
         <v>0.8901239846088072</v>
       </c>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
+      <c r="X17" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.9154337885245184</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.9210139898107688</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.8317307692307693</v>
+      </c>
       <c r="AB17" t="n">
         <v>0.9885</v>
       </c>
@@ -2265,10 +2289,18 @@
       <c r="AI17" t="n">
         <v>0.9793038570084666</v>
       </c>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
+      <c r="AJ17" t="n">
+        <v>0.9535</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.9635020514235886</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.9665507292992196</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.9177718832891246</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -2324,14 +2356,30 @@
       <c r="S18" t="n">
         <v>0.9431711145996859</v>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>0.8925</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.8833001430703827</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.8815152148486854</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.9011494252873564</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.9175</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.9369200077183196</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.9429282310741</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.8467966573816156</v>
+      </c>
       <c r="AB18" t="n">
         <v>0.992</v>
       </c>
@@ -2344,14 +2392,30 @@
       <c r="AE18" t="n">
         <v>0.9947019867549668</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
+      <c r="AF18" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.9591789085531396</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.9589712476674036</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.9612555174104952</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.9595</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.9692629935669244</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.9726519262699764</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.918429003021148</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -2395,30 +2459,78 @@
       <c r="O19" t="n">
         <v>0.5337078651685393</v>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.9135475922098584</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.902289897537076</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.9698360655737704</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.9005</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.8927419605149616</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.8914608646822619</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.9055529188419554</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.8575</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.8842973300320611</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.8919684340854805</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9575</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.9186120529762056</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.907921055750218</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.9720670391061452</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.9465</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.945134354103176</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.9449579632107644</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.9468982630272952</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.959201996691999</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.9631740489967182</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.8996212121212122</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -6368,10 +6480,18 @@
       <c r="C54" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="D54" t="n">
+        <v>67.34999999999999</v>
+      </c>
+      <c r="E54" t="n">
+        <v>14.5098</v>
+      </c>
+      <c r="F54" t="n">
+        <v>13.3144</v>
+      </c>
+      <c r="G54" t="n">
+        <v>80.2568</v>
+      </c>
       <c r="H54" t="n">
         <v>66.40000000000001</v>
       </c>
@@ -11230,10 +11350,18 @@
       <c r="C96" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="D96" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="E96" t="n">
+        <v>12.5681</v>
+      </c>
+      <c r="F96" t="n">
+        <v>12.6525</v>
+      </c>
+      <c r="G96" t="n">
+        <v>11.5556</v>
+      </c>
       <c r="H96" t="n">
         <v>20.61</v>
       </c>
@@ -11337,14 +11465,30 @@
       <c r="C97" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+      <c r="D97" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="E97" t="n">
+        <v>14.8782</v>
+      </c>
+      <c r="F97" t="n">
+        <v>14.7854</v>
+      </c>
+      <c r="G97" t="n">
+        <v>15.8996</v>
+      </c>
+      <c r="H97" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="I97" t="n">
+        <v>15.0822</v>
+      </c>
+      <c r="J97" t="n">
+        <v>14.8466</v>
+      </c>
+      <c r="K97" t="n">
+        <v>20.5011</v>
+      </c>
       <c r="L97" t="n">
         <v>56.53</v>
       </c>
@@ -11436,10 +11580,18 @@
       <c r="C98" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+      <c r="D98" t="n">
+        <v>40</v>
+      </c>
+      <c r="E98" t="n">
+        <v>13.6643</v>
+      </c>
+      <c r="F98" t="n">
+        <v>9.789300000000001</v>
+      </c>
+      <c r="G98" t="n">
+        <v>56.2893</v>
+      </c>
       <c r="H98" t="n">
         <v>32.04</v>
       </c>
@@ -31935,10 +32087,18 @@
       <c r="C275" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
+      <c r="D275" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="E275" t="n">
+        <v>65.3908</v>
+      </c>
+      <c r="F275" t="n">
+        <v>65.27809999999999</v>
+      </c>
+      <c r="G275" t="n">
+        <v>66.2921</v>
+      </c>
       <c r="H275" t="n">
         <v>67.75</v>
       </c>
@@ -32042,18 +32202,42 @@
       <c r="C276" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr"/>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="inlineStr"/>
-      <c r="N276" t="inlineStr"/>
-      <c r="O276" t="inlineStr"/>
+      <c r="D276" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="E276" t="n">
+        <v>26.257</v>
+      </c>
+      <c r="F276" t="n">
+        <v>23.0223</v>
+      </c>
+      <c r="G276" t="n">
+        <v>52.1348</v>
+      </c>
+      <c r="H276" t="n">
+        <v>33.55</v>
+      </c>
+      <c r="I276" t="n">
+        <v>43.2631</v>
+      </c>
+      <c r="J276" t="n">
+        <v>44.6205</v>
+      </c>
+      <c r="K276" t="n">
+        <v>21.544</v>
+      </c>
+      <c r="L276" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="M276" t="n">
+        <v>44.4045</v>
+      </c>
+      <c r="N276" t="n">
+        <v>44.9889</v>
+      </c>
+      <c r="O276" t="n">
+        <v>30.9623</v>
+      </c>
       <c r="P276" t="n">
         <v>87.26000000000001</v>
       </c>
@@ -32133,18 +32317,42 @@
       <c r="C277" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="inlineStr"/>
-      <c r="N277" t="inlineStr"/>
-      <c r="O277" t="inlineStr"/>
+      <c r="D277" t="n">
+        <v>84.66</v>
+      </c>
+      <c r="E277" t="n">
+        <v>37.408</v>
+      </c>
+      <c r="F277" t="n">
+        <v>30.5326</v>
+      </c>
+      <c r="G277" t="n">
+        <v>92.4117</v>
+      </c>
+      <c r="H277" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="I277" t="n">
+        <v>39.9571</v>
+      </c>
+      <c r="J277" t="n">
+        <v>39.6664</v>
+      </c>
+      <c r="K277" t="n">
+        <v>44.6086</v>
+      </c>
+      <c r="L277" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="M277" t="n">
+        <v>43.1468</v>
+      </c>
+      <c r="N277" t="n">
+        <v>43.6684</v>
+      </c>
+      <c r="O277" t="n">
+        <v>31.1512</v>
+      </c>
       <c r="P277" t="n">
         <v>45.38</v>
       </c>
@@ -32224,14 +32432,30 @@
       <c r="C278" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr"/>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
+      <c r="D278" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="E278" t="n">
+        <v>40.2369</v>
+      </c>
+      <c r="F278" t="n">
+        <v>38.8733</v>
+      </c>
+      <c r="G278" t="n">
+        <v>51.146</v>
+      </c>
+      <c r="H278" t="n">
+        <v>52.54</v>
+      </c>
+      <c r="I278" t="n">
+        <v>43.4439</v>
+      </c>
+      <c r="J278" t="n">
+        <v>43.0034</v>
+      </c>
+      <c r="K278" t="n">
+        <v>50.4918</v>
+      </c>
       <c r="L278" t="n">
         <v>63.2</v>
       </c>
@@ -32323,10 +32547,18 @@
       <c r="C279" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D279" t="inlineStr"/>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
+      <c r="D279" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="E279" t="n">
+        <v>23.2932</v>
+      </c>
+      <c r="F279" t="n">
+        <v>18.7791</v>
+      </c>
+      <c r="G279" t="n">
+        <v>59.4059</v>
+      </c>
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr"/>
@@ -32343,10 +32575,18 @@
       <c r="O279" t="n">
         <v>63.2143</v>
       </c>
-      <c r="P279" t="inlineStr"/>
-      <c r="Q279" t="inlineStr"/>
-      <c r="R279" t="inlineStr"/>
-      <c r="S279" t="inlineStr"/>
+      <c r="P279" t="n">
+        <v>51.37</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>33.0077</v>
+      </c>
+      <c r="R279" t="n">
+        <v>29.0807</v>
+      </c>
+      <c r="S279" t="n">
+        <v>64.42310000000001</v>
+      </c>
       <c r="T279" t="n">
         <v>88.3</v>
       </c>
@@ -35773,10 +36013,18 @@
       <c r="C309" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr"/>
-      <c r="F309" t="inlineStr"/>
-      <c r="G309" t="inlineStr"/>
+      <c r="D309" t="n">
+        <v>0.035064935064935</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0.0421853943949084</v>
+      </c>
+      <c r="F309" t="n">
+        <v>0.0470967741935483</v>
+      </c>
+      <c r="G309" t="n">
+        <v>0.0028943560057887</v>
+      </c>
       <c r="H309" t="n">
         <v>0.122077922077922</v>
       </c>
@@ -42261,18 +42509,42 @@
       <c r="C365" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D365" t="inlineStr"/>
-      <c r="E365" t="inlineStr"/>
-      <c r="F365" t="inlineStr"/>
-      <c r="G365" t="inlineStr"/>
-      <c r="H365" t="inlineStr"/>
-      <c r="I365" t="inlineStr"/>
-      <c r="J365" t="inlineStr"/>
-      <c r="K365" t="inlineStr"/>
-      <c r="L365" t="inlineStr"/>
-      <c r="M365" t="inlineStr"/>
-      <c r="N365" t="inlineStr"/>
-      <c r="O365" t="inlineStr"/>
+      <c r="D365" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="E365" t="n">
+        <v>38.555</v>
+      </c>
+      <c r="F365" t="n">
+        <v>40.0985</v>
+      </c>
+      <c r="G365" t="n">
+        <v>32.381</v>
+      </c>
+      <c r="H365" t="n">
+        <v>45.62</v>
+      </c>
+      <c r="I365" t="n">
+        <v>55.4078</v>
+      </c>
+      <c r="J365" t="n">
+        <v>57.5574</v>
+      </c>
+      <c r="K365" t="n">
+        <v>38.2114</v>
+      </c>
+      <c r="L365" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="M365" t="n">
+        <v>49.773</v>
+      </c>
+      <c r="N365" t="n">
+        <v>53.6177</v>
+      </c>
+      <c r="O365" t="n">
+        <v>3.6364</v>
+      </c>
       <c r="P365" t="n">
         <v>62.84</v>
       </c>
@@ -42352,18 +42624,42 @@
       <c r="C366" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D366" t="inlineStr"/>
-      <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr"/>
-      <c r="G366" t="inlineStr"/>
-      <c r="H366" t="inlineStr"/>
-      <c r="I366" t="inlineStr"/>
-      <c r="J366" t="inlineStr"/>
-      <c r="K366" t="inlineStr"/>
-      <c r="L366" t="inlineStr"/>
-      <c r="M366" t="inlineStr"/>
-      <c r="N366" t="inlineStr"/>
-      <c r="O366" t="inlineStr"/>
+      <c r="D366" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="E366" t="n">
+        <v>43.5106</v>
+      </c>
+      <c r="F366" t="n">
+        <v>42.1375</v>
+      </c>
+      <c r="G366" t="n">
+        <v>49.0028</v>
+      </c>
+      <c r="H366" t="n">
+        <v>45.92</v>
+      </c>
+      <c r="I366" t="n">
+        <v>22.2452</v>
+      </c>
+      <c r="J366" t="n">
+        <v>17.6409</v>
+      </c>
+      <c r="K366" t="n">
+        <v>59.0799</v>
+      </c>
+      <c r="L366" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="M366" t="n">
+        <v>44.7288</v>
+      </c>
+      <c r="N366" t="n">
+        <v>45.9275</v>
+      </c>
+      <c r="O366" t="n">
+        <v>30.3448</v>
+      </c>
       <c r="P366" t="n">
         <v>36.86</v>
       </c>
@@ -42443,18 +42739,42 @@
       <c r="C367" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D367" t="inlineStr"/>
-      <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr"/>
-      <c r="G367" t="inlineStr"/>
-      <c r="H367" t="inlineStr"/>
-      <c r="I367" t="inlineStr"/>
-      <c r="J367" t="inlineStr"/>
-      <c r="K367" t="inlineStr"/>
-      <c r="L367" t="inlineStr"/>
-      <c r="M367" t="inlineStr"/>
-      <c r="N367" t="inlineStr"/>
-      <c r="O367" t="inlineStr"/>
+      <c r="D367" t="n">
+        <v>47.13</v>
+      </c>
+      <c r="E367" t="n">
+        <v>44.6968</v>
+      </c>
+      <c r="F367" t="n">
+        <v>41.9083</v>
+      </c>
+      <c r="G367" t="n">
+        <v>55.8511</v>
+      </c>
+      <c r="H367" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="I367" t="n">
+        <v>44.5855</v>
+      </c>
+      <c r="J367" t="n">
+        <v>44.6251</v>
+      </c>
+      <c r="K367" t="n">
+        <v>44.2688</v>
+      </c>
+      <c r="L367" t="n">
+        <v>44.41</v>
+      </c>
+      <c r="M367" t="n">
+        <v>49.8753</v>
+      </c>
+      <c r="N367" t="n">
+        <v>51.6506</v>
+      </c>
+      <c r="O367" t="n">
+        <v>28.5714</v>
+      </c>
       <c r="P367" t="n">
         <v>43.81</v>
       </c>
@@ -42534,18 +42854,42 @@
       <c r="C368" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D368" t="inlineStr"/>
-      <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
-      <c r="G368" t="inlineStr"/>
-      <c r="H368" t="inlineStr"/>
-      <c r="I368" t="inlineStr"/>
-      <c r="J368" t="inlineStr"/>
-      <c r="K368" t="inlineStr"/>
-      <c r="L368" t="inlineStr"/>
-      <c r="M368" t="inlineStr"/>
-      <c r="N368" t="inlineStr"/>
-      <c r="O368" t="inlineStr"/>
+      <c r="D368" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="E368" t="n">
+        <v>34.8961</v>
+      </c>
+      <c r="F368" t="n">
+        <v>31.5967</v>
+      </c>
+      <c r="G368" t="n">
+        <v>48.0938</v>
+      </c>
+      <c r="H368" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="I368" t="n">
+        <v>39.6648</v>
+      </c>
+      <c r="J368" t="n">
+        <v>39.1607</v>
+      </c>
+      <c r="K368" t="n">
+        <v>43.6975</v>
+      </c>
+      <c r="L368" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="M368" t="n">
+        <v>40.8979</v>
+      </c>
+      <c r="N368" t="n">
+        <v>41.9604</v>
+      </c>
+      <c r="O368" t="n">
+        <v>28.1481</v>
+      </c>
       <c r="P368" t="n">
         <v>45.62</v>
       </c>
@@ -42625,18 +42969,42 @@
       <c r="C369" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D369" t="inlineStr"/>
-      <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr"/>
-      <c r="G369" t="inlineStr"/>
-      <c r="H369" t="inlineStr"/>
-      <c r="I369" t="inlineStr"/>
-      <c r="J369" t="inlineStr"/>
-      <c r="K369" t="inlineStr"/>
-      <c r="L369" t="inlineStr"/>
-      <c r="M369" t="inlineStr"/>
-      <c r="N369" t="inlineStr"/>
-      <c r="O369" t="inlineStr"/>
+      <c r="D369" t="n">
+        <v>40.18</v>
+      </c>
+      <c r="E369" t="n">
+        <v>35.0114</v>
+      </c>
+      <c r="F369" t="n">
+        <v>31.5619</v>
+      </c>
+      <c r="G369" t="n">
+        <v>48.8095</v>
+      </c>
+      <c r="H369" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="I369" t="n">
+        <v>46.2271</v>
+      </c>
+      <c r="J369" t="n">
+        <v>47.6721</v>
+      </c>
+      <c r="K369" t="n">
+        <v>34.6667</v>
+      </c>
+      <c r="L369" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="M369" t="n">
+        <v>50.051</v>
+      </c>
+      <c r="N369" t="n">
+        <v>50.6125</v>
+      </c>
+      <c r="O369" t="n">
+        <v>43.3121</v>
+      </c>
       <c r="P369" t="n">
         <v>56.5</v>
       </c>
@@ -45615,10 +45983,18 @@
       <c r="C395" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D395" t="inlineStr"/>
-      <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr"/>
-      <c r="G395" t="inlineStr"/>
+      <c r="D395" t="n">
+        <v>0.7552870090634441</v>
+      </c>
+      <c r="E395" t="n">
+        <v>0.1721170395869191</v>
+      </c>
+      <c r="F395" t="n">
+        <v>0</v>
+      </c>
+      <c r="G395" t="n">
+        <v>0.8605851979345955</v>
+      </c>
       <c r="H395" t="n">
         <v>0.5105740181268882</v>
       </c>
@@ -45722,10 +46098,18 @@
       <c r="C396" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D396" t="inlineStr"/>
-      <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr"/>
-      <c r="G396" t="inlineStr"/>
+      <c r="D396" t="n">
+        <v>0.7522658610271903</v>
+      </c>
+      <c r="E396" t="n">
+        <v>0.1717241379310345</v>
+      </c>
+      <c r="F396" t="n">
+        <v>0</v>
+      </c>
+      <c r="G396" t="n">
+        <v>0.8586206896551725</v>
+      </c>
       <c r="H396" t="n">
         <v>0.5287009063444109</v>
       </c>
@@ -45829,10 +46213,18 @@
       <c r="C397" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D397" t="inlineStr"/>
-      <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
-      <c r="G397" t="inlineStr"/>
+      <c r="D397" t="n">
+        <v>0.7583081570996979</v>
+      </c>
+      <c r="E397" t="n">
+        <v>0.1725085910652921</v>
+      </c>
+      <c r="F397" t="n">
+        <v>0</v>
+      </c>
+      <c r="G397" t="n">
+        <v>0.8625429553264605</v>
+      </c>
       <c r="H397" t="n">
         <v>0.5105740181268882</v>
       </c>
@@ -45845,10 +46237,18 @@
       <c r="K397" t="n">
         <v>0.6680327868852459</v>
       </c>
-      <c r="L397" t="inlineStr"/>
-      <c r="M397" t="inlineStr"/>
-      <c r="N397" t="inlineStr"/>
-      <c r="O397" t="inlineStr"/>
+      <c r="L397" t="n">
+        <v>0.2809667673716012</v>
+      </c>
+      <c r="M397" t="n">
+        <v>0.0760741594871029</v>
+      </c>
+      <c r="N397" t="n">
+        <v>0.0472194980204133</v>
+      </c>
+      <c r="O397" t="n">
+        <v>0.4223300970873786</v>
+      </c>
       <c r="P397" t="n">
         <v>0.7552870090634441</v>
       </c>
@@ -45873,10 +46273,18 @@
       <c r="W397" t="n">
         <v>0.7532467532467533</v>
       </c>
-      <c r="X397" t="inlineStr"/>
-      <c r="Y397" t="inlineStr"/>
-      <c r="Z397" t="inlineStr"/>
-      <c r="AA397" t="inlineStr"/>
+      <c r="X397" t="n">
+        <v>0.5770392749244713</v>
+      </c>
+      <c r="Y397" t="n">
+        <v>0.5994015463394461</v>
+      </c>
+      <c r="Z397" t="n">
+        <v>0.6069274327768243</v>
+      </c>
+      <c r="AA397" t="n">
+        <v>0.509090909090909</v>
+      </c>
       <c r="AB397" t="n">
         <v>0.7824773413897281</v>
       </c>
@@ -45920,10 +46328,18 @@
       <c r="C398" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D398" t="inlineStr"/>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr"/>
+      <c r="D398" t="n">
+        <v>0.7462235649546828</v>
+      </c>
+      <c r="E398" t="n">
+        <v>0.1709342560553633</v>
+      </c>
+      <c r="F398" t="n">
+        <v>0</v>
+      </c>
+      <c r="G398" t="n">
+        <v>0.8546712802768166</v>
+      </c>
       <c r="H398" t="n">
         <v>0.513595166163142</v>
       </c>
@@ -46027,10 +46443,18 @@
       <c r="C399" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D399" t="inlineStr"/>
-      <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
-      <c r="G399" t="inlineStr"/>
+      <c r="D399" t="n">
+        <v>0.743202416918429</v>
+      </c>
+      <c r="E399" t="n">
+        <v>0.1705372616984402</v>
+      </c>
+      <c r="F399" t="n">
+        <v>0</v>
+      </c>
+      <c r="G399" t="n">
+        <v>0.8526863084922011</v>
+      </c>
       <c r="H399" t="n">
         <v>0.4984894259818731</v>
       </c>
